--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nk365-my.sharepoint.com/personal/ss80751_ad_nkc_co_jp/Documents/ドキュメント/Work_Vault/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10360" documentId="13_ncr:1_{22133521-4050-492C-8145-0AE2EA6E1C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8209AE7-992F-4B35-B121-83C758419604}"/>
+  <xr:revisionPtr revIDLastSave="10362" documentId="13_ncr:1_{22133521-4050-492C-8145-0AE2EA6E1C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{410EB5A4-5E7A-4387-8134-E05B441F776E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="18" r:id="rId1"/>
@@ -2083,79 +2083,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2197,6 +2124,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1"/>
@@ -2208,6 +2144,70 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7318,102 +7318,102 @@
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="27"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="51"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="93"/>
       <c r="W1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="52" t="s">
+      <c r="X1" s="94" t="s">
         <v>336</v>
       </c>
-      <c r="Y1" s="53"/>
+      <c r="Y1" s="95"/>
     </row>
     <row r="2" spans="1:25" ht="58.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="30"/>
       <c r="B2" s="31"/>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="96" t="s">
         <v>337</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
       <c r="X2" s="32"/>
       <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
       <c r="B3" s="34"/>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="98" t="s">
         <v>338</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="98"/>
+      <c r="U3" s="98"/>
+      <c r="V3" s="98"/>
+      <c r="W3" s="98"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="35"/>
     </row>
     <row r="4" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
       <c r="B4" s="34"/>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="98" t="s">
         <v>339</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="98"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="98"/>
+      <c r="W4" s="98"/>
       <c r="X4" s="34"/>
       <c r="Y4" s="35"/>
     </row>
@@ -7457,21 +7457,21 @@
       <c r="K6" s="34"/>
       <c r="L6" s="37"/>
       <c r="M6" s="37"/>
-      <c r="O6" s="49" t="s">
+      <c r="O6" s="91" t="s">
         <v>340</v>
       </c>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="49" t="s">
+      <c r="P6" s="92"/>
+      <c r="Q6" s="93"/>
+      <c r="R6" s="91" t="s">
         <v>341</v>
       </c>
-      <c r="S6" s="50"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="49" t="s">
+      <c r="S6" s="92"/>
+      <c r="T6" s="93"/>
+      <c r="U6" s="91" t="s">
         <v>342</v>
       </c>
-      <c r="V6" s="50"/>
-      <c r="W6" s="51"/>
+      <c r="V6" s="92"/>
+      <c r="W6" s="93"/>
       <c r="Y6" s="35"/>
     </row>
     <row r="7" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7488,15 +7488,15 @@
       <c r="K7" s="34"/>
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="63"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="65"/>
-      <c r="U7" s="63"/>
-      <c r="V7" s="64"/>
-      <c r="W7" s="65"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="84"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="84"/>
+      <c r="U7" s="82"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="84"/>
       <c r="Y7" s="35"/>
     </row>
     <row r="8" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7513,15 +7513,15 @@
       <c r="K8" s="34"/>
       <c r="L8" s="37"/>
       <c r="M8" s="37"/>
-      <c r="O8" s="66"/>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="68"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="67"/>
-      <c r="T8" s="68"/>
-      <c r="U8" s="66"/>
-      <c r="V8" s="67"/>
-      <c r="W8" s="68"/>
+      <c r="O8" s="85"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="87"/>
+      <c r="R8" s="85"/>
+      <c r="S8" s="86"/>
+      <c r="T8" s="87"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="86"/>
+      <c r="W8" s="87"/>
       <c r="Y8" s="35"/>
     </row>
     <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7565,18 +7565,18 @@
       <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="N10" s="37"/>
-      <c r="P10" s="69" t="s">
+      <c r="P10" s="88" t="s">
         <v>343</v>
       </c>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="70" t="s">
+      <c r="Q10" s="88"/>
+      <c r="R10" s="88"/>
+      <c r="S10" s="89" t="s">
         <v>344</v>
       </c>
-      <c r="T10" s="70"/>
-      <c r="U10" s="70"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="70"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="89"/>
+      <c r="W10" s="89"/>
       <c r="Y10" s="35"/>
     </row>
     <row r="11" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7594,27 +7594,27 @@
       <c r="L11" s="37"/>
       <c r="M11" s="37"/>
       <c r="N11" s="37"/>
-      <c r="P11" s="57" t="s">
+      <c r="P11" s="80" t="s">
         <v>345</v>
       </c>
-      <c r="Q11" s="57"/>
-      <c r="R11" s="57"/>
-      <c r="S11" s="71" t="s">
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="90" t="s">
         <v>344</v>
       </c>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="71"/>
+      <c r="T11" s="90"/>
+      <c r="U11" s="90"/>
+      <c r="V11" s="90"/>
+      <c r="W11" s="90"/>
       <c r="Y11" s="35"/>
     </row>
     <row r="12" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="38"/>
-      <c r="P12" s="57" t="s">
+      <c r="P12" s="80" t="s">
         <v>346</v>
       </c>
-      <c r="Q12" s="57"/>
-      <c r="R12" s="57"/>
+      <c r="Q12" s="80"/>
+      <c r="R12" s="80"/>
       <c r="S12" s="39"/>
       <c r="T12" s="39"/>
       <c r="U12" s="40" t="s">
@@ -7636,642 +7636,642 @@
         <v>349</v>
       </c>
       <c r="B14" s="45"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61"/>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="59"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="57"/>
-      <c r="V14" s="57"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="58"/>
-      <c r="Y14" s="59"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="76"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="76"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="79"/>
+      <c r="T14" s="78"/>
+      <c r="U14" s="80"/>
+      <c r="V14" s="80"/>
+      <c r="W14" s="79"/>
+      <c r="X14" s="78"/>
+      <c r="Y14" s="79"/>
     </row>
     <row r="15" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B15" s="45"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="58"/>
-      <c r="S15" s="59"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="57"/>
-      <c r="V15" s="57"/>
-      <c r="W15" s="59"/>
-      <c r="X15" s="58"/>
-      <c r="Y15" s="59"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="76"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="76"/>
+      <c r="P15" s="76"/>
+      <c r="Q15" s="77"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="79"/>
+      <c r="T15" s="78"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="79"/>
+      <c r="X15" s="78"/>
+      <c r="Y15" s="79"/>
     </row>
     <row r="16" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B16" s="45"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="61"/>
-      <c r="M16" s="61"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="61"/>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="62"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="59"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="57"/>
-      <c r="V16" s="57"/>
-      <c r="W16" s="59"/>
-      <c r="X16" s="58"/>
-      <c r="Y16" s="59"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="76"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="76"/>
+      <c r="P16" s="76"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="78"/>
+      <c r="S16" s="79"/>
+      <c r="T16" s="78"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="79"/>
+      <c r="X16" s="78"/>
+      <c r="Y16" s="79"/>
     </row>
     <row r="17" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B17" s="45"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="61"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="61"/>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="62"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="59"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="57"/>
-      <c r="V17" s="57"/>
-      <c r="W17" s="59"/>
-      <c r="X17" s="58"/>
-      <c r="Y17" s="59"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="76"/>
+      <c r="M17" s="76"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="76"/>
+      <c r="P17" s="76"/>
+      <c r="Q17" s="77"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="79"/>
+      <c r="T17" s="78"/>
+      <c r="U17" s="80"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="79"/>
+      <c r="X17" s="78"/>
+      <c r="Y17" s="79"/>
     </row>
     <row r="18" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B18" s="45"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="61"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="57"/>
-      <c r="V18" s="57"/>
-      <c r="W18" s="59"/>
-      <c r="X18" s="58"/>
-      <c r="Y18" s="59"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="79"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="76"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="76"/>
+      <c r="P18" s="76"/>
+      <c r="Q18" s="77"/>
+      <c r="R18" s="78"/>
+      <c r="S18" s="79"/>
+      <c r="T18" s="78"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="79"/>
+      <c r="X18" s="78"/>
+      <c r="Y18" s="79"/>
     </row>
     <row r="19" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B19" s="45"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="61"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="62"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="59"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="59"/>
-      <c r="X19" s="58"/>
-      <c r="Y19" s="59"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="76"/>
+      <c r="M19" s="76"/>
+      <c r="N19" s="76"/>
+      <c r="O19" s="76"/>
+      <c r="P19" s="76"/>
+      <c r="Q19" s="77"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="79"/>
+      <c r="T19" s="78"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="79"/>
+      <c r="X19" s="78"/>
+      <c r="Y19" s="79"/>
     </row>
     <row r="20" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B20" s="45"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="59"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="57"/>
-      <c r="V20" s="57"/>
-      <c r="W20" s="59"/>
-      <c r="X20" s="58"/>
-      <c r="Y20" s="59"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="76"/>
+      <c r="M20" s="76"/>
+      <c r="N20" s="76"/>
+      <c r="O20" s="76"/>
+      <c r="P20" s="76"/>
+      <c r="Q20" s="77"/>
+      <c r="R20" s="78"/>
+      <c r="S20" s="79"/>
+      <c r="T20" s="78"/>
+      <c r="U20" s="80"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="79"/>
+      <c r="X20" s="78"/>
+      <c r="Y20" s="79"/>
     </row>
     <row r="21" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B21" s="45"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="61"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="61"/>
-      <c r="O21" s="61"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="62"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="58"/>
-      <c r="U21" s="57"/>
-      <c r="V21" s="57"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="58"/>
-      <c r="Y21" s="59"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="76"/>
+      <c r="M21" s="76"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="76"/>
+      <c r="P21" s="76"/>
+      <c r="Q21" s="77"/>
+      <c r="R21" s="78"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="78"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="79"/>
+      <c r="X21" s="78"/>
+      <c r="Y21" s="79"/>
     </row>
     <row r="22" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B22" s="45"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="61"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="58"/>
-      <c r="U22" s="57"/>
-      <c r="V22" s="57"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="58"/>
-      <c r="Y22" s="59"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="79"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="76"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="76"/>
+      <c r="P22" s="76"/>
+      <c r="Q22" s="77"/>
+      <c r="R22" s="78"/>
+      <c r="S22" s="79"/>
+      <c r="T22" s="78"/>
+      <c r="U22" s="80"/>
+      <c r="V22" s="80"/>
+      <c r="W22" s="79"/>
+      <c r="X22" s="78"/>
+      <c r="Y22" s="79"/>
     </row>
     <row r="23" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B23" s="45"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="59"/>
-      <c r="T23" s="58"/>
-      <c r="U23" s="57"/>
-      <c r="V23" s="57"/>
-      <c r="W23" s="59"/>
-      <c r="X23" s="58"/>
-      <c r="Y23" s="59"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="76"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="76"/>
+      <c r="P23" s="76"/>
+      <c r="Q23" s="77"/>
+      <c r="R23" s="78"/>
+      <c r="S23" s="79"/>
+      <c r="T23" s="78"/>
+      <c r="U23" s="80"/>
+      <c r="V23" s="80"/>
+      <c r="W23" s="79"/>
+      <c r="X23" s="78"/>
+      <c r="Y23" s="79"/>
     </row>
     <row r="24" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B24" s="45"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="61"/>
-      <c r="O24" s="61"/>
-      <c r="P24" s="61"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="59"/>
-      <c r="T24" s="58"/>
-      <c r="U24" s="57"/>
-      <c r="V24" s="57"/>
-      <c r="W24" s="59"/>
-      <c r="X24" s="58"/>
-      <c r="Y24" s="59"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="76"/>
+      <c r="M24" s="76"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="77"/>
+      <c r="R24" s="78"/>
+      <c r="S24" s="79"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="80"/>
+      <c r="V24" s="80"/>
+      <c r="W24" s="79"/>
+      <c r="X24" s="78"/>
+      <c r="Y24" s="79"/>
     </row>
     <row r="25" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B25" s="45"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="61"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="61"/>
-      <c r="O25" s="61"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="62"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="59"/>
-      <c r="T25" s="58"/>
-      <c r="U25" s="57"/>
-      <c r="V25" s="57"/>
-      <c r="W25" s="59"/>
-      <c r="X25" s="58"/>
-      <c r="Y25" s="59"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="76"/>
+      <c r="M25" s="76"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="76"/>
+      <c r="Q25" s="77"/>
+      <c r="R25" s="78"/>
+      <c r="S25" s="79"/>
+      <c r="T25" s="78"/>
+      <c r="U25" s="80"/>
+      <c r="V25" s="80"/>
+      <c r="W25" s="79"/>
+      <c r="X25" s="78"/>
+      <c r="Y25" s="79"/>
     </row>
     <row r="26" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B26" s="45"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
-      <c r="O26" s="61"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="58"/>
-      <c r="S26" s="59"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="57"/>
-      <c r="V26" s="57"/>
-      <c r="W26" s="59"/>
-      <c r="X26" s="58"/>
-      <c r="Y26" s="59"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="79"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="76"/>
+      <c r="M26" s="76"/>
+      <c r="N26" s="76"/>
+      <c r="O26" s="76"/>
+      <c r="P26" s="76"/>
+      <c r="Q26" s="77"/>
+      <c r="R26" s="78"/>
+      <c r="S26" s="79"/>
+      <c r="T26" s="78"/>
+      <c r="U26" s="80"/>
+      <c r="V26" s="80"/>
+      <c r="W26" s="79"/>
+      <c r="X26" s="78"/>
+      <c r="Y26" s="79"/>
     </row>
     <row r="27" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B27" s="45"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="61"/>
-      <c r="O27" s="61"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="59"/>
-      <c r="T27" s="58"/>
-      <c r="U27" s="57"/>
-      <c r="V27" s="57"/>
-      <c r="W27" s="59"/>
-      <c r="X27" s="58"/>
-      <c r="Y27" s="59"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="79"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="80"/>
+      <c r="J27" s="79"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="76"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="76"/>
+      <c r="P27" s="76"/>
+      <c r="Q27" s="77"/>
+      <c r="R27" s="78"/>
+      <c r="S27" s="79"/>
+      <c r="T27" s="78"/>
+      <c r="U27" s="80"/>
+      <c r="V27" s="80"/>
+      <c r="W27" s="79"/>
+      <c r="X27" s="78"/>
+      <c r="Y27" s="79"/>
     </row>
     <row r="28" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B28" s="45"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="61"/>
-      <c r="O28" s="61"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="62"/>
-      <c r="R28" s="58"/>
-      <c r="S28" s="59"/>
-      <c r="T28" s="58"/>
-      <c r="U28" s="57"/>
-      <c r="V28" s="57"/>
-      <c r="W28" s="59"/>
-      <c r="X28" s="58"/>
-      <c r="Y28" s="59"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="76"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="76"/>
+      <c r="P28" s="76"/>
+      <c r="Q28" s="77"/>
+      <c r="R28" s="78"/>
+      <c r="S28" s="79"/>
+      <c r="T28" s="78"/>
+      <c r="U28" s="80"/>
+      <c r="V28" s="80"/>
+      <c r="W28" s="79"/>
+      <c r="X28" s="78"/>
+      <c r="Y28" s="79"/>
     </row>
     <row r="29" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B29" s="45"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="59"/>
-      <c r="K29" s="60"/>
-      <c r="L29" s="61"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="61"/>
-      <c r="O29" s="61"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="62"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="59"/>
-      <c r="T29" s="58"/>
-      <c r="U29" s="57"/>
-      <c r="V29" s="57"/>
-      <c r="W29" s="59"/>
-      <c r="X29" s="58"/>
-      <c r="Y29" s="59"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="76"/>
+      <c r="M29" s="76"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="76"/>
+      <c r="P29" s="76"/>
+      <c r="Q29" s="77"/>
+      <c r="R29" s="78"/>
+      <c r="S29" s="79"/>
+      <c r="T29" s="78"/>
+      <c r="U29" s="80"/>
+      <c r="V29" s="80"/>
+      <c r="W29" s="79"/>
+      <c r="X29" s="78"/>
+      <c r="Y29" s="79"/>
     </row>
     <row r="30" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
         <v>349</v>
       </c>
       <c r="B30" s="45"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="60"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="62"/>
-      <c r="R30" s="58"/>
-      <c r="S30" s="59"/>
-      <c r="T30" s="58"/>
-      <c r="U30" s="57"/>
-      <c r="V30" s="57"/>
-      <c r="W30" s="59"/>
-      <c r="X30" s="58"/>
-      <c r="Y30" s="59"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="76"/>
+      <c r="M30" s="76"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="76"/>
+      <c r="Q30" s="77"/>
+      <c r="R30" s="78"/>
+      <c r="S30" s="79"/>
+      <c r="T30" s="78"/>
+      <c r="U30" s="80"/>
+      <c r="V30" s="80"/>
+      <c r="W30" s="79"/>
+      <c r="X30" s="78"/>
+      <c r="Y30" s="79"/>
     </row>
     <row r="31" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="44"/>
       <c r="B31" s="45"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="60"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="59"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="57"/>
-      <c r="V31" s="57"/>
-      <c r="W31" s="59"/>
-      <c r="X31" s="58"/>
-      <c r="Y31" s="59"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="76"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="77"/>
+      <c r="R31" s="78"/>
+      <c r="S31" s="79"/>
+      <c r="T31" s="78"/>
+      <c r="U31" s="80"/>
+      <c r="V31" s="80"/>
+      <c r="W31" s="79"/>
+      <c r="X31" s="78"/>
+      <c r="Y31" s="79"/>
     </row>
     <row r="32" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="45"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="74"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="67"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="68"/>
       <c r="K32" s="75"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="61"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="61"/>
-      <c r="P32" s="61"/>
-      <c r="Q32" s="62"/>
-      <c r="R32" s="58"/>
-      <c r="S32" s="59"/>
-      <c r="T32" s="58"/>
-      <c r="U32" s="57"/>
-      <c r="V32" s="57"/>
-      <c r="W32" s="59"/>
-      <c r="X32" s="58"/>
-      <c r="Y32" s="59"/>
+      <c r="L32" s="76"/>
+      <c r="M32" s="76"/>
+      <c r="N32" s="76"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="76"/>
+      <c r="Q32" s="77"/>
+      <c r="R32" s="78"/>
+      <c r="S32" s="79"/>
+      <c r="T32" s="78"/>
+      <c r="U32" s="80"/>
+      <c r="V32" s="80"/>
+      <c r="W32" s="79"/>
+      <c r="X32" s="78"/>
+      <c r="Y32" s="79"/>
     </row>
     <row r="33" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="46"/>
       <c r="B33" s="47"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="73"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="93"/>
-      <c r="L33" s="94"/>
-      <c r="M33" s="94"/>
-      <c r="N33" s="94"/>
-      <c r="O33" s="94"/>
-      <c r="P33" s="94"/>
-      <c r="Q33" s="95"/>
-      <c r="R33" s="96"/>
-      <c r="S33" s="97"/>
-      <c r="T33" s="96"/>
-      <c r="U33" s="98"/>
-      <c r="V33" s="98"/>
-      <c r="W33" s="97"/>
-      <c r="X33" s="96"/>
-      <c r="Y33" s="97"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="67"/>
+      <c r="I33" s="67"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="72"/>
+      <c r="S33" s="73"/>
+      <c r="T33" s="72"/>
+      <c r="U33" s="74"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="73"/>
+      <c r="X33" s="72"/>
+      <c r="Y33" s="73"/>
     </row>
     <row r="34" spans="1:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="76" t="s">
+      <c r="A34" s="49" t="s">
         <v>350</v>
       </c>
-      <c r="B34" s="77"/>
-      <c r="C34" s="80" t="s">
+      <c r="B34" s="50"/>
+      <c r="C34" s="53" t="s">
         <v>351</v>
       </c>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="80" t="s">
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="53" t="s">
         <v>352</v>
       </c>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="82"/>
-      <c r="K34" s="76" t="s">
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="49" t="s">
         <v>353</v>
       </c>
-      <c r="L34" s="86"/>
-      <c r="M34" s="86"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="86"/>
-      <c r="P34" s="86"/>
-      <c r="Q34" s="87"/>
-      <c r="R34" s="76" t="s">
+      <c r="L34" s="59"/>
+      <c r="M34" s="59"/>
+      <c r="N34" s="59"/>
+      <c r="O34" s="59"/>
+      <c r="P34" s="59"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="49" t="s">
         <v>354</v>
       </c>
-      <c r="S34" s="77"/>
-      <c r="T34" s="76" t="s">
+      <c r="S34" s="50"/>
+      <c r="T34" s="49" t="s">
         <v>355</v>
       </c>
-      <c r="U34" s="91"/>
-      <c r="V34" s="91"/>
-      <c r="W34" s="77"/>
-      <c r="X34" s="76" t="s">
+      <c r="U34" s="64"/>
+      <c r="V34" s="64"/>
+      <c r="W34" s="50"/>
+      <c r="X34" s="49" t="s">
         <v>356</v>
       </c>
-      <c r="Y34" s="77"/>
+      <c r="Y34" s="50"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A35" s="78"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="84"/>
-      <c r="J35" s="85"/>
-      <c r="K35" s="88"/>
-      <c r="L35" s="89"/>
-      <c r="M35" s="89"/>
-      <c r="N35" s="89"/>
-      <c r="O35" s="89"/>
-      <c r="P35" s="89"/>
-      <c r="Q35" s="90"/>
-      <c r="R35" s="78"/>
-      <c r="S35" s="79"/>
-      <c r="T35" s="78"/>
-      <c r="U35" s="92"/>
-      <c r="V35" s="92"/>
-      <c r="W35" s="79"/>
-      <c r="X35" s="78"/>
-      <c r="Y35" s="79"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="63"/>
+      <c r="R35" s="51"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="51"/>
+      <c r="U35" s="65"/>
+      <c r="V35" s="65"/>
+      <c r="W35" s="52"/>
+      <c r="X35" s="51"/>
+      <c r="Y35" s="52"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="s">
@@ -8286,115 +8286,22 @@
     </row>
   </sheetData>
   <mergeCells count="143">
-    <mergeCell ref="X34:Y35"/>
-    <mergeCell ref="A34:B35"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G34:J35"/>
-    <mergeCell ref="K34:Q35"/>
-    <mergeCell ref="R34:S35"/>
-    <mergeCell ref="T34:W35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="K33:Q33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="T33:W33"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="T32:W32"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:W31"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="T30:W30"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:W29"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:W28"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:W27"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="X25:Y25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:W23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:W22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="O7:Q8"/>
+    <mergeCell ref="R7:T8"/>
+    <mergeCell ref="U7:W8"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="S10:W10"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="D2:W2"/>
+    <mergeCell ref="D3:W3"/>
+    <mergeCell ref="D4:W4"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="U6:W6"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="K16:Q16"/>
@@ -8413,22 +8320,115 @@
     <mergeCell ref="K14:Q14"/>
     <mergeCell ref="R14:S14"/>
     <mergeCell ref="T14:W14"/>
-    <mergeCell ref="O7:Q8"/>
-    <mergeCell ref="R7:T8"/>
-    <mergeCell ref="U7:W8"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="S10:W10"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="D2:W2"/>
-    <mergeCell ref="D3:W3"/>
-    <mergeCell ref="D4:W4"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:T6"/>
-    <mergeCell ref="U6:W6"/>
-    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:W22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:W23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="T26:W26"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:W28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:W27"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="T30:W30"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:W29"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="T32:W32"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:W31"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X34:Y35"/>
+    <mergeCell ref="A34:B35"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G34:J35"/>
+    <mergeCell ref="K34:Q35"/>
+    <mergeCell ref="R34:S35"/>
+    <mergeCell ref="T34:W35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="K33:Q33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="T33:W33"/>
+    <mergeCell ref="X33:Y33"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.86614173228346458" right="0.51181102362204722" top="0.59055118110236227" bottom="0.19685039370078741" header="0.59055118110236227" footer="0.19685039370078741"/>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nk365-my.sharepoint.com/personal/ss80751_ad_nkc_co_jp/Documents/ドキュメント/Work_Vault/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10560" documentId="13_ncr:1_{22133521-4050-492C-8145-0AE2EA6E1C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54665DF-4627-41DD-A35E-F812ED673D25}"/>
+  <xr:revisionPtr revIDLastSave="10562" documentId="13_ncr:1_{22133521-4050-492C-8145-0AE2EA6E1C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7262B560-2756-4609-88E1-6181B043A5FC}"/>
   <bookViews>
     <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="10500" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2188,6 +2188,79 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2229,15 +2302,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1"/>
@@ -2248,70 +2312,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9249,62 +9249,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>72543</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>83649</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="82" name="直線矢印コネクタ 81">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FFF3187-F921-FB77-6305-90F78AAFA168}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3699663" y="17678400"/>
-          <a:ext cx="917886" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>122848</xdr:colOff>
       <xdr:row>99</xdr:row>
@@ -9477,6 +9421,63 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>72543</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>83650</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直線矢印コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74335EB5-48FF-944E-D451-9C056391D61A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3699663" y="17678400"/>
+          <a:ext cx="917887" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd type="none"/>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10433,102 +10434,102 @@
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="27"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="120"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="92"/>
       <c r="W1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="113" t="s">
+      <c r="X1" s="93" t="s">
         <v>298</v>
       </c>
-      <c r="Y1" s="114"/>
+      <c r="Y1" s="94"/>
     </row>
     <row r="2" spans="1:25" ht="58.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="30"/>
       <c r="B2" s="31"/>
-      <c r="D2" s="115" t="s">
+      <c r="D2" s="95" t="s">
         <v>299</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116"/>
-      <c r="T2" s="116"/>
-      <c r="U2" s="116"/>
-      <c r="V2" s="116"/>
-      <c r="W2" s="116"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="96"/>
+      <c r="U2" s="96"/>
+      <c r="V2" s="96"/>
+      <c r="W2" s="96"/>
       <c r="X2" s="32"/>
       <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
       <c r="B3" s="34"/>
-      <c r="D3" s="117" t="s">
+      <c r="D3" s="97" t="s">
         <v>300</v>
       </c>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="117"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="117"/>
-      <c r="U3" s="117"/>
-      <c r="V3" s="117"/>
-      <c r="W3" s="117"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="97"/>
+      <c r="W3" s="97"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="35"/>
     </row>
     <row r="4" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
       <c r="B4" s="34"/>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="97" t="s">
         <v>301</v>
       </c>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="117"/>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="117"/>
-      <c r="V4" s="117"/>
-      <c r="W4" s="117"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="97"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="97"/>
+      <c r="S4" s="97"/>
+      <c r="T4" s="97"/>
+      <c r="U4" s="97"/>
+      <c r="V4" s="97"/>
+      <c r="W4" s="97"/>
       <c r="X4" s="34"/>
       <c r="Y4" s="35"/>
     </row>
@@ -10572,21 +10573,21 @@
       <c r="K6" s="34"/>
       <c r="L6" s="37"/>
       <c r="M6" s="37"/>
-      <c r="O6" s="118" t="s">
+      <c r="O6" s="90" t="s">
         <v>302</v>
       </c>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="120"/>
-      <c r="R6" s="118" t="s">
+      <c r="P6" s="91"/>
+      <c r="Q6" s="92"/>
+      <c r="R6" s="90" t="s">
         <v>303</v>
       </c>
-      <c r="S6" s="119"/>
-      <c r="T6" s="120"/>
-      <c r="U6" s="118" t="s">
+      <c r="S6" s="91"/>
+      <c r="T6" s="92"/>
+      <c r="U6" s="90" t="s">
         <v>304</v>
       </c>
-      <c r="V6" s="119"/>
-      <c r="W6" s="120"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="92"/>
       <c r="Y6" s="35"/>
     </row>
     <row r="7" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10603,15 +10604,15 @@
       <c r="K7" s="34"/>
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
-      <c r="O7" s="121"/>
-      <c r="P7" s="122"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="121"/>
-      <c r="S7" s="122"/>
-      <c r="T7" s="123"/>
-      <c r="U7" s="121"/>
-      <c r="V7" s="122"/>
-      <c r="W7" s="123"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="82"/>
+      <c r="Q7" s="83"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="82"/>
+      <c r="T7" s="83"/>
+      <c r="U7" s="81"/>
+      <c r="V7" s="82"/>
+      <c r="W7" s="83"/>
       <c r="Y7" s="35"/>
     </row>
     <row r="8" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10628,15 +10629,15 @@
       <c r="K8" s="34"/>
       <c r="L8" s="37"/>
       <c r="M8" s="37"/>
-      <c r="O8" s="124"/>
-      <c r="P8" s="125"/>
-      <c r="Q8" s="126"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="126"/>
-      <c r="U8" s="124"/>
-      <c r="V8" s="125"/>
-      <c r="W8" s="126"/>
+      <c r="O8" s="84"/>
+      <c r="P8" s="85"/>
+      <c r="Q8" s="86"/>
+      <c r="R8" s="84"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="86"/>
+      <c r="U8" s="84"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="86"/>
       <c r="Y8" s="35"/>
     </row>
     <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10680,18 +10681,18 @@
       <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="N10" s="37"/>
-      <c r="P10" s="127" t="s">
+      <c r="P10" s="87" t="s">
         <v>305</v>
       </c>
-      <c r="Q10" s="127"/>
-      <c r="R10" s="127"/>
-      <c r="S10" s="128" t="s">
+      <c r="Q10" s="87"/>
+      <c r="R10" s="87"/>
+      <c r="S10" s="88" t="s">
         <v>306</v>
       </c>
-      <c r="T10" s="128"/>
-      <c r="U10" s="128"/>
-      <c r="V10" s="128"/>
-      <c r="W10" s="128"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="88"/>
+      <c r="W10" s="88"/>
       <c r="Y10" s="35"/>
     </row>
     <row r="11" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10709,27 +10710,27 @@
       <c r="L11" s="37"/>
       <c r="M11" s="37"/>
       <c r="N11" s="37"/>
-      <c r="P11" s="111" t="s">
+      <c r="P11" s="80" t="s">
         <v>307</v>
       </c>
-      <c r="Q11" s="111"/>
-      <c r="R11" s="111"/>
-      <c r="S11" s="129" t="s">
+      <c r="Q11" s="80"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="89" t="s">
         <v>306</v>
       </c>
-      <c r="T11" s="129"/>
-      <c r="U11" s="129"/>
-      <c r="V11" s="129"/>
-      <c r="W11" s="129"/>
+      <c r="T11" s="89"/>
+      <c r="U11" s="89"/>
+      <c r="V11" s="89"/>
+      <c r="W11" s="89"/>
       <c r="Y11" s="35"/>
     </row>
     <row r="12" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="38"/>
-      <c r="P12" s="111" t="s">
+      <c r="P12" s="80" t="s">
         <v>308</v>
       </c>
-      <c r="Q12" s="111"/>
-      <c r="R12" s="111"/>
+      <c r="Q12" s="80"/>
+      <c r="R12" s="80"/>
       <c r="S12" s="39"/>
       <c r="T12" s="39"/>
       <c r="U12" s="40" t="s">
@@ -10751,642 +10752,642 @@
         <v>311</v>
       </c>
       <c r="B14" s="45"/>
-      <c r="C14" s="109"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="107"/>
-      <c r="M14" s="107"/>
-      <c r="N14" s="107"/>
-      <c r="O14" s="107"/>
-      <c r="P14" s="107"/>
-      <c r="Q14" s="108"/>
-      <c r="R14" s="109"/>
-      <c r="S14" s="110"/>
-      <c r="T14" s="109"/>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111"/>
-      <c r="W14" s="110"/>
-      <c r="X14" s="109"/>
-      <c r="Y14" s="110"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="100"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="101"/>
+      <c r="N14" s="101"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="101"/>
+      <c r="Q14" s="102"/>
+      <c r="R14" s="98"/>
+      <c r="S14" s="99"/>
+      <c r="T14" s="98"/>
+      <c r="U14" s="80"/>
+      <c r="V14" s="80"/>
+      <c r="W14" s="99"/>
+      <c r="X14" s="98"/>
+      <c r="Y14" s="99"/>
     </row>
     <row r="15" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B15" s="45"/>
-      <c r="C15" s="109"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="109"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="112"/>
-      <c r="L15" s="107"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="107"/>
-      <c r="O15" s="107"/>
-      <c r="P15" s="107"/>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="109"/>
-      <c r="S15" s="110"/>
-      <c r="T15" s="109"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-      <c r="W15" s="110"/>
-      <c r="X15" s="109"/>
-      <c r="Y15" s="110"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="100"/>
+      <c r="L15" s="101"/>
+      <c r="M15" s="101"/>
+      <c r="N15" s="101"/>
+      <c r="O15" s="101"/>
+      <c r="P15" s="101"/>
+      <c r="Q15" s="102"/>
+      <c r="R15" s="98"/>
+      <c r="S15" s="99"/>
+      <c r="T15" s="98"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="99"/>
+      <c r="X15" s="98"/>
+      <c r="Y15" s="99"/>
     </row>
     <row r="16" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B16" s="45"/>
-      <c r="C16" s="109"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="110"/>
-      <c r="G16" s="109"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="112"/>
-      <c r="L16" s="107"/>
-      <c r="M16" s="107"/>
-      <c r="N16" s="107"/>
-      <c r="O16" s="107"/>
-      <c r="P16" s="107"/>
-      <c r="Q16" s="108"/>
-      <c r="R16" s="109"/>
-      <c r="S16" s="110"/>
-      <c r="T16" s="109"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="109"/>
-      <c r="Y16" s="110"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="100"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="101"/>
+      <c r="N16" s="101"/>
+      <c r="O16" s="101"/>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="102"/>
+      <c r="R16" s="98"/>
+      <c r="S16" s="99"/>
+      <c r="T16" s="98"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="99"/>
+      <c r="X16" s="98"/>
+      <c r="Y16" s="99"/>
     </row>
     <row r="17" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B17" s="45"/>
-      <c r="C17" s="109"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="112"/>
-      <c r="L17" s="107"/>
-      <c r="M17" s="107"/>
-      <c r="N17" s="107"/>
-      <c r="O17" s="107"/>
-      <c r="P17" s="107"/>
-      <c r="Q17" s="108"/>
-      <c r="R17" s="109"/>
-      <c r="S17" s="110"/>
-      <c r="T17" s="109"/>
-      <c r="U17" s="111"/>
-      <c r="V17" s="111"/>
-      <c r="W17" s="110"/>
-      <c r="X17" s="109"/>
-      <c r="Y17" s="110"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="101"/>
+      <c r="N17" s="101"/>
+      <c r="O17" s="101"/>
+      <c r="P17" s="101"/>
+      <c r="Q17" s="102"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="99"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="80"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="99"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="99"/>
     </row>
     <row r="18" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B18" s="45"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="111"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="112"/>
-      <c r="L18" s="107"/>
-      <c r="M18" s="107"/>
-      <c r="N18" s="107"/>
-      <c r="O18" s="107"/>
-      <c r="P18" s="107"/>
-      <c r="Q18" s="108"/>
-      <c r="R18" s="109"/>
-      <c r="S18" s="110"/>
-      <c r="T18" s="109"/>
-      <c r="U18" s="111"/>
-      <c r="V18" s="111"/>
-      <c r="W18" s="110"/>
-      <c r="X18" s="109"/>
-      <c r="Y18" s="110"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="99"/>
+      <c r="K18" s="100"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="101"/>
+      <c r="N18" s="101"/>
+      <c r="O18" s="101"/>
+      <c r="P18" s="101"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="99"/>
+      <c r="T18" s="98"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="99"/>
+      <c r="X18" s="98"/>
+      <c r="Y18" s="99"/>
     </row>
     <row r="19" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B19" s="45"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="109"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="107"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="109"/>
-      <c r="S19" s="110"/>
-      <c r="T19" s="109"/>
-      <c r="U19" s="111"/>
-      <c r="V19" s="111"/>
-      <c r="W19" s="110"/>
-      <c r="X19" s="109"/>
-      <c r="Y19" s="110"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="101"/>
+      <c r="O19" s="101"/>
+      <c r="P19" s="101"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="98"/>
+      <c r="S19" s="99"/>
+      <c r="T19" s="98"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="99"/>
+      <c r="X19" s="98"/>
+      <c r="Y19" s="99"/>
     </row>
     <row r="20" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B20" s="45"/>
-      <c r="C20" s="109"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="107"/>
-      <c r="M20" s="107"/>
-      <c r="N20" s="107"/>
-      <c r="O20" s="107"/>
-      <c r="P20" s="107"/>
-      <c r="Q20" s="108"/>
-      <c r="R20" s="109"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="109"/>
-      <c r="U20" s="111"/>
-      <c r="V20" s="111"/>
-      <c r="W20" s="110"/>
-      <c r="X20" s="109"/>
-      <c r="Y20" s="110"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="99"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="101"/>
+      <c r="N20" s="101"/>
+      <c r="O20" s="101"/>
+      <c r="P20" s="101"/>
+      <c r="Q20" s="102"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="99"/>
+      <c r="T20" s="98"/>
+      <c r="U20" s="80"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="99"/>
+      <c r="X20" s="98"/>
+      <c r="Y20" s="99"/>
     </row>
     <row r="21" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B21" s="45"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="112"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="107"/>
-      <c r="N21" s="107"/>
-      <c r="O21" s="107"/>
-      <c r="P21" s="107"/>
-      <c r="Q21" s="108"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="110"/>
-      <c r="T21" s="109"/>
-      <c r="U21" s="111"/>
-      <c r="V21" s="111"/>
-      <c r="W21" s="110"/>
-      <c r="X21" s="109"/>
-      <c r="Y21" s="110"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="99"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="101"/>
+      <c r="N21" s="101"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="101"/>
+      <c r="Q21" s="102"/>
+      <c r="R21" s="98"/>
+      <c r="S21" s="99"/>
+      <c r="T21" s="98"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="99"/>
+      <c r="X21" s="98"/>
+      <c r="Y21" s="99"/>
     </row>
     <row r="22" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B22" s="45"/>
-      <c r="C22" s="109"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="110"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="112"/>
-      <c r="L22" s="107"/>
-      <c r="M22" s="107"/>
-      <c r="N22" s="107"/>
-      <c r="O22" s="107"/>
-      <c r="P22" s="107"/>
-      <c r="Q22" s="108"/>
-      <c r="R22" s="109"/>
-      <c r="S22" s="110"/>
-      <c r="T22" s="109"/>
-      <c r="U22" s="111"/>
-      <c r="V22" s="111"/>
-      <c r="W22" s="110"/>
-      <c r="X22" s="109"/>
-      <c r="Y22" s="110"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="100"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="101"/>
+      <c r="N22" s="101"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="101"/>
+      <c r="Q22" s="102"/>
+      <c r="R22" s="98"/>
+      <c r="S22" s="99"/>
+      <c r="T22" s="98"/>
+      <c r="U22" s="80"/>
+      <c r="V22" s="80"/>
+      <c r="W22" s="99"/>
+      <c r="X22" s="98"/>
+      <c r="Y22" s="99"/>
     </row>
     <row r="23" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B23" s="45"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="109"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="107"/>
-      <c r="M23" s="107"/>
-      <c r="N23" s="107"/>
-      <c r="O23" s="107"/>
-      <c r="P23" s="107"/>
-      <c r="Q23" s="108"/>
-      <c r="R23" s="109"/>
-      <c r="S23" s="110"/>
-      <c r="T23" s="109"/>
-      <c r="U23" s="111"/>
-      <c r="V23" s="111"/>
-      <c r="W23" s="110"/>
-      <c r="X23" s="109"/>
-      <c r="Y23" s="110"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="101"/>
+      <c r="N23" s="101"/>
+      <c r="O23" s="101"/>
+      <c r="P23" s="101"/>
+      <c r="Q23" s="102"/>
+      <c r="R23" s="98"/>
+      <c r="S23" s="99"/>
+      <c r="T23" s="98"/>
+      <c r="U23" s="80"/>
+      <c r="V23" s="80"/>
+      <c r="W23" s="99"/>
+      <c r="X23" s="98"/>
+      <c r="Y23" s="99"/>
     </row>
     <row r="24" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B24" s="45"/>
-      <c r="C24" s="109"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="107"/>
-      <c r="M24" s="107"/>
-      <c r="N24" s="107"/>
-      <c r="O24" s="107"/>
-      <c r="P24" s="107"/>
-      <c r="Q24" s="108"/>
-      <c r="R24" s="109"/>
-      <c r="S24" s="110"/>
-      <c r="T24" s="109"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="110"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="110"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="101"/>
+      <c r="N24" s="101"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="101"/>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="98"/>
+      <c r="S24" s="99"/>
+      <c r="T24" s="98"/>
+      <c r="U24" s="80"/>
+      <c r="V24" s="80"/>
+      <c r="W24" s="99"/>
+      <c r="X24" s="98"/>
+      <c r="Y24" s="99"/>
     </row>
     <row r="25" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B25" s="45"/>
-      <c r="C25" s="109"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="112"/>
-      <c r="L25" s="107"/>
-      <c r="M25" s="107"/>
-      <c r="N25" s="107"/>
-      <c r="O25" s="107"/>
-      <c r="P25" s="107"/>
-      <c r="Q25" s="108"/>
-      <c r="R25" s="109"/>
-      <c r="S25" s="110"/>
-      <c r="T25" s="109"/>
-      <c r="U25" s="111"/>
-      <c r="V25" s="111"/>
-      <c r="W25" s="110"/>
-      <c r="X25" s="109"/>
-      <c r="Y25" s="110"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="101"/>
+      <c r="N25" s="101"/>
+      <c r="O25" s="101"/>
+      <c r="P25" s="101"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="98"/>
+      <c r="S25" s="99"/>
+      <c r="T25" s="98"/>
+      <c r="U25" s="80"/>
+      <c r="V25" s="80"/>
+      <c r="W25" s="99"/>
+      <c r="X25" s="98"/>
+      <c r="Y25" s="99"/>
     </row>
     <row r="26" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B26" s="45"/>
-      <c r="C26" s="109"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="109"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="107"/>
-      <c r="M26" s="107"/>
-      <c r="N26" s="107"/>
-      <c r="O26" s="107"/>
-      <c r="P26" s="107"/>
-      <c r="Q26" s="108"/>
-      <c r="R26" s="109"/>
-      <c r="S26" s="110"/>
-      <c r="T26" s="109"/>
-      <c r="U26" s="111"/>
-      <c r="V26" s="111"/>
-      <c r="W26" s="110"/>
-      <c r="X26" s="109"/>
-      <c r="Y26" s="110"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="101"/>
+      <c r="N26" s="101"/>
+      <c r="O26" s="101"/>
+      <c r="P26" s="101"/>
+      <c r="Q26" s="102"/>
+      <c r="R26" s="98"/>
+      <c r="S26" s="99"/>
+      <c r="T26" s="98"/>
+      <c r="U26" s="80"/>
+      <c r="V26" s="80"/>
+      <c r="W26" s="99"/>
+      <c r="X26" s="98"/>
+      <c r="Y26" s="99"/>
     </row>
     <row r="27" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B27" s="45"/>
-      <c r="C27" s="109"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="112"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="107"/>
-      <c r="N27" s="107"/>
-      <c r="O27" s="107"/>
-      <c r="P27" s="107"/>
-      <c r="Q27" s="108"/>
-      <c r="R27" s="109"/>
-      <c r="S27" s="110"/>
-      <c r="T27" s="109"/>
-      <c r="U27" s="111"/>
-      <c r="V27" s="111"/>
-      <c r="W27" s="110"/>
-      <c r="X27" s="109"/>
-      <c r="Y27" s="110"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="80"/>
+      <c r="J27" s="99"/>
+      <c r="K27" s="100"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="101"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="101"/>
+      <c r="Q27" s="102"/>
+      <c r="R27" s="98"/>
+      <c r="S27" s="99"/>
+      <c r="T27" s="98"/>
+      <c r="U27" s="80"/>
+      <c r="V27" s="80"/>
+      <c r="W27" s="99"/>
+      <c r="X27" s="98"/>
+      <c r="Y27" s="99"/>
     </row>
     <row r="28" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B28" s="45"/>
-      <c r="C28" s="109"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="112"/>
-      <c r="L28" s="107"/>
-      <c r="M28" s="107"/>
-      <c r="N28" s="107"/>
-      <c r="O28" s="107"/>
-      <c r="P28" s="107"/>
-      <c r="Q28" s="108"/>
-      <c r="R28" s="109"/>
-      <c r="S28" s="110"/>
-      <c r="T28" s="109"/>
-      <c r="U28" s="111"/>
-      <c r="V28" s="111"/>
-      <c r="W28" s="110"/>
-      <c r="X28" s="109"/>
-      <c r="Y28" s="110"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="98"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="99"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="101"/>
+      <c r="N28" s="101"/>
+      <c r="O28" s="101"/>
+      <c r="P28" s="101"/>
+      <c r="Q28" s="102"/>
+      <c r="R28" s="98"/>
+      <c r="S28" s="99"/>
+      <c r="T28" s="98"/>
+      <c r="U28" s="80"/>
+      <c r="V28" s="80"/>
+      <c r="W28" s="99"/>
+      <c r="X28" s="98"/>
+      <c r="Y28" s="99"/>
     </row>
     <row r="29" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B29" s="45"/>
-      <c r="C29" s="109"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="109"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="112"/>
-      <c r="L29" s="107"/>
-      <c r="M29" s="107"/>
-      <c r="N29" s="107"/>
-      <c r="O29" s="107"/>
-      <c r="P29" s="107"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="109"/>
-      <c r="S29" s="110"/>
-      <c r="T29" s="109"/>
-      <c r="U29" s="111"/>
-      <c r="V29" s="111"/>
-      <c r="W29" s="110"/>
-      <c r="X29" s="109"/>
-      <c r="Y29" s="110"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="99"/>
+      <c r="K29" s="100"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="101"/>
+      <c r="N29" s="101"/>
+      <c r="O29" s="101"/>
+      <c r="P29" s="101"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="99"/>
+      <c r="T29" s="98"/>
+      <c r="U29" s="80"/>
+      <c r="V29" s="80"/>
+      <c r="W29" s="99"/>
+      <c r="X29" s="98"/>
+      <c r="Y29" s="99"/>
     </row>
     <row r="30" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B30" s="45"/>
-      <c r="C30" s="109"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="109"/>
-      <c r="H30" s="111"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="112"/>
-      <c r="L30" s="107"/>
-      <c r="M30" s="107"/>
-      <c r="N30" s="107"/>
-      <c r="O30" s="107"/>
-      <c r="P30" s="107"/>
-      <c r="Q30" s="108"/>
-      <c r="R30" s="109"/>
-      <c r="S30" s="110"/>
-      <c r="T30" s="109"/>
-      <c r="U30" s="111"/>
-      <c r="V30" s="111"/>
-      <c r="W30" s="110"/>
-      <c r="X30" s="109"/>
-      <c r="Y30" s="110"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="99"/>
+      <c r="K30" s="100"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="101"/>
+      <c r="N30" s="101"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="101"/>
+      <c r="Q30" s="102"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="99"/>
+      <c r="T30" s="98"/>
+      <c r="U30" s="80"/>
+      <c r="V30" s="80"/>
+      <c r="W30" s="99"/>
+      <c r="X30" s="98"/>
+      <c r="Y30" s="99"/>
     </row>
     <row r="31" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="44"/>
       <c r="B31" s="45"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="107"/>
-      <c r="N31" s="107"/>
-      <c r="O31" s="107"/>
-      <c r="P31" s="107"/>
-      <c r="Q31" s="108"/>
-      <c r="R31" s="109"/>
-      <c r="S31" s="110"/>
-      <c r="T31" s="109"/>
-      <c r="U31" s="111"/>
-      <c r="V31" s="111"/>
-      <c r="W31" s="110"/>
-      <c r="X31" s="109"/>
-      <c r="Y31" s="110"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="105"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="101"/>
+      <c r="N31" s="101"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="101"/>
+      <c r="Q31" s="102"/>
+      <c r="R31" s="98"/>
+      <c r="S31" s="99"/>
+      <c r="T31" s="98"/>
+      <c r="U31" s="80"/>
+      <c r="V31" s="80"/>
+      <c r="W31" s="99"/>
+      <c r="X31" s="98"/>
+      <c r="Y31" s="99"/>
     </row>
     <row r="32" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="45"/>
-      <c r="C32" s="97"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="99"/>
-      <c r="G32" s="97"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="99"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="105"/>
       <c r="K32" s="106"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="107"/>
-      <c r="N32" s="107"/>
-      <c r="O32" s="107"/>
-      <c r="P32" s="107"/>
-      <c r="Q32" s="108"/>
-      <c r="R32" s="109"/>
-      <c r="S32" s="110"/>
-      <c r="T32" s="109"/>
-      <c r="U32" s="111"/>
-      <c r="V32" s="111"/>
-      <c r="W32" s="110"/>
-      <c r="X32" s="109"/>
-      <c r="Y32" s="110"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="101"/>
+      <c r="N32" s="101"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="102"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="99"/>
+      <c r="T32" s="98"/>
+      <c r="U32" s="80"/>
+      <c r="V32" s="80"/>
+      <c r="W32" s="99"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="99"/>
     </row>
     <row r="33" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="46"/>
       <c r="B33" s="47"/>
-      <c r="C33" s="97"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="97"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="98"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="100"/>
-      <c r="L33" s="101"/>
-      <c r="M33" s="101"/>
-      <c r="N33" s="101"/>
-      <c r="O33" s="101"/>
-      <c r="P33" s="101"/>
-      <c r="Q33" s="102"/>
-      <c r="R33" s="103"/>
-      <c r="S33" s="104"/>
-      <c r="T33" s="103"/>
-      <c r="U33" s="105"/>
-      <c r="V33" s="105"/>
-      <c r="W33" s="104"/>
-      <c r="X33" s="103"/>
-      <c r="Y33" s="104"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="105"/>
+      <c r="K33" s="124"/>
+      <c r="L33" s="125"/>
+      <c r="M33" s="125"/>
+      <c r="N33" s="125"/>
+      <c r="O33" s="125"/>
+      <c r="P33" s="125"/>
+      <c r="Q33" s="126"/>
+      <c r="R33" s="127"/>
+      <c r="S33" s="128"/>
+      <c r="T33" s="127"/>
+      <c r="U33" s="129"/>
+      <c r="V33" s="129"/>
+      <c r="W33" s="128"/>
+      <c r="X33" s="127"/>
+      <c r="Y33" s="128"/>
     </row>
     <row r="34" spans="1:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="80" t="s">
+      <c r="A34" s="107" t="s">
         <v>312</v>
       </c>
-      <c r="B34" s="81"/>
-      <c r="C34" s="84" t="s">
+      <c r="B34" s="108"/>
+      <c r="C34" s="111" t="s">
         <v>313</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="84" t="s">
+      <c r="D34" s="112"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="113"/>
+      <c r="G34" s="111" t="s">
         <v>314</v>
       </c>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="86"/>
-      <c r="K34" s="80" t="s">
+      <c r="H34" s="112"/>
+      <c r="I34" s="112"/>
+      <c r="J34" s="113"/>
+      <c r="K34" s="107" t="s">
         <v>315</v>
       </c>
-      <c r="L34" s="90"/>
-      <c r="M34" s="90"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="90"/>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="91"/>
-      <c r="R34" s="80" t="s">
+      <c r="L34" s="117"/>
+      <c r="M34" s="117"/>
+      <c r="N34" s="117"/>
+      <c r="O34" s="117"/>
+      <c r="P34" s="117"/>
+      <c r="Q34" s="118"/>
+      <c r="R34" s="107" t="s">
         <v>316</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="80" t="s">
+      <c r="S34" s="108"/>
+      <c r="T34" s="107" t="s">
         <v>317</v>
       </c>
-      <c r="U34" s="95"/>
-      <c r="V34" s="95"/>
-      <c r="W34" s="81"/>
-      <c r="X34" s="80" t="s">
+      <c r="U34" s="122"/>
+      <c r="V34" s="122"/>
+      <c r="W34" s="108"/>
+      <c r="X34" s="107" t="s">
         <v>318</v>
       </c>
-      <c r="Y34" s="81"/>
+      <c r="Y34" s="108"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A35" s="82"/>
-      <c r="B35" s="83"/>
-      <c r="C35" s="87"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="87"/>
-      <c r="H35" s="88"/>
-      <c r="I35" s="88"/>
-      <c r="J35" s="89"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="93"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="93"/>
-      <c r="P35" s="93"/>
-      <c r="Q35" s="94"/>
-      <c r="R35" s="82"/>
-      <c r="S35" s="83"/>
-      <c r="T35" s="82"/>
-      <c r="U35" s="96"/>
-      <c r="V35" s="96"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="82"/>
-      <c r="Y35" s="83"/>
+      <c r="A35" s="109"/>
+      <c r="B35" s="110"/>
+      <c r="C35" s="114"/>
+      <c r="D35" s="115"/>
+      <c r="E35" s="115"/>
+      <c r="F35" s="116"/>
+      <c r="G35" s="114"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="115"/>
+      <c r="J35" s="116"/>
+      <c r="K35" s="119"/>
+      <c r="L35" s="120"/>
+      <c r="M35" s="120"/>
+      <c r="N35" s="120"/>
+      <c r="O35" s="120"/>
+      <c r="P35" s="120"/>
+      <c r="Q35" s="121"/>
+      <c r="R35" s="109"/>
+      <c r="S35" s="110"/>
+      <c r="T35" s="109"/>
+      <c r="U35" s="123"/>
+      <c r="V35" s="123"/>
+      <c r="W35" s="110"/>
+      <c r="X35" s="109"/>
+      <c r="Y35" s="110"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="s">
@@ -11401,15 +11402,116 @@
     </row>
   </sheetData>
   <mergeCells count="143">
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="O7:Q8"/>
-    <mergeCell ref="R7:T8"/>
-    <mergeCell ref="U7:W8"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="S10:W10"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="X34:Y35"/>
+    <mergeCell ref="A34:B35"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G34:J35"/>
+    <mergeCell ref="K34:Q35"/>
+    <mergeCell ref="R34:S35"/>
+    <mergeCell ref="T34:W35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="K33:Q33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="T33:W33"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="T32:W32"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:W31"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="T30:W30"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:W29"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:W28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:W27"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="T26:W26"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:W23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:W22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:Y17"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="D2:W2"/>
     <mergeCell ref="D3:W3"/>
@@ -11434,116 +11536,15 @@
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="K14:Q14"/>
     <mergeCell ref="R14:S14"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:W22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:W23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="X25:Y25"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:W28"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:W27"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="T30:W30"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:W29"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="T32:W32"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:W31"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="X34:Y35"/>
-    <mergeCell ref="A34:B35"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G34:J35"/>
-    <mergeCell ref="K34:Q35"/>
-    <mergeCell ref="R34:S35"/>
-    <mergeCell ref="T34:W35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="K33:Q33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="T33:W33"/>
-    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="O7:Q8"/>
+    <mergeCell ref="R7:T8"/>
+    <mergeCell ref="U7:W8"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="S10:W10"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.86614173228346458" right="0.51181102362204722" top="0.59055118110236227" bottom="0.19685039370078741" header="0.59055118110236227" footer="0.19685039370078741"/>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nk365-my.sharepoint.com/personal/ss80751_ad_nkc_co_jp/Documents/ドキュメント/Work_Vault/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10562" documentId="13_ncr:1_{22133521-4050-492C-8145-0AE2EA6E1C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7262B560-2756-4609-88E1-6181B043A5FC}"/>
+  <xr:revisionPtr revIDLastSave="10571" documentId="13_ncr:1_{22133521-4050-492C-8145-0AE2EA6E1C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6822FB3-74A6-4247-A275-5810271DAE47}"/>
   <bookViews>
     <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="10500" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7411,14 +7411,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>97155</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>10160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>41453</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>10160</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7433,7 +7433,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1651635" y="16268700"/>
+          <a:off x="1651635" y="15913100"/>
           <a:ext cx="462458" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -7472,8 +7472,8 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>41453</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>10160</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7489,7 +7489,7 @@
       <xdr:spPr>
         <a:xfrm flipV="1">
           <a:off x="2114093" y="12420600"/>
-          <a:ext cx="0" cy="3848100"/>
+          <a:ext cx="0" cy="3492500"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -7498,62 +7498,6 @@
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>41453</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>44044</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="58" name="直線矢印コネクタ 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FFDCE70-2121-69C6-F2E7-C5AE17056E00}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2114093" y="12420600"/>
-          <a:ext cx="132131" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -9480,6 +9424,62 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>41453</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>44044</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Arrow Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBA0C8A6-D7E4-3171-86D9-D5D83986E374}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2114093" y="12420600"/>
+          <a:ext cx="132131" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nk365-my.sharepoint.com/personal/ss80751_ad_nkc_co_jp/Documents/ドキュメント/Work_Vault/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss80751\AppData\Local\Temp\kohden-code\kanri_tejun_work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10571" documentId="13_ncr:1_{22133521-4050-492C-8145-0AE2EA6E1C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6822FB3-74A6-4247-A275-5810271DAE47}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC963946-1E0E-4B79-95BF-70F924E5A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="10500" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="10500" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="18" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="会議課題一覧(一時)" sheetId="14" r:id="rId11"/>
     <sheet name="付録 引用元と確認範囲" sheetId="15" r:id="rId12"/>
     <sheet name="要確認事項一覧" sheetId="16" r:id="rId13"/>
+    <sheet name="7-5仮_サービス起動停止" sheetId="19" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="5">月次再起動!$A$1:$AZ$100</definedName>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="385">
   <si>
     <t>手 順 書</t>
   </si>
@@ -1391,6 +1392,65 @@
   </si>
   <si>
     <t>本文との差分：なし(2026-10-23 に第7章7-4 を本原文の完全引用に変更)。パスワード2か所のみ「［認証情報：伏字］」への置換で、windwos をはじめ原文の表記はそのまま。図解の様式はマウントプログラム(DGS)の手順書0494-913473 のフローチャートによる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7. 異常時の対応(仮)</t>
+  </si>
+  <si>
+    <t>PanaCIMサービスの起動・停止・再起動(ベンダー取扱説明書からの完全引用・仮実装)</t>
+  </si>
+  <si>
+    <t>位置づけ：第7章7-4(異常時のサーバー再起動、出典0494-912039(06))の補助として、PanaCIM関連サービスの一元的な開始・停止・再起動の手順をベンダー取扱説明書から引用する。会議方針(第1回記録行22)の完全引用対象は0494-912039(06)であり、本シートは仮実装(未承認)。本採用の可否は会議(2026-10-28)での判断事項とする。</t>
+  </si>
+  <si>
+    <t>6.3 サービスコントローラー</t>
+  </si>
+  <si>
+    <t>PanaCIM アプリケーションサーバーの様々なサービスを一元管理します。</t>
+  </si>
+  <si>
+    <t>操作</t>
+  </si>
+  <si>
+    <t>スタート&gt;プログラム&gt;Panasonic&gt;PanaCIM&gt;PanaCIM Services&gt;サービスコントローラーの順にクリックします。</t>
+  </si>
+  <si>
+    <t>システムトレイにあるPanaCIMサービスコントローラーのアイコンをクリックし起動します。</t>
+  </si>
+  <si>
+    <t>画面左上のボタンを選択すると、全てのPanaCIMサービスを開始/停止/再起動します。</t>
+  </si>
+  <si>
+    <t>画面右上のボタンを選択すると、各サービスを個別に開始/停止/再起動します。またこのセクションでシミュレータを設定/モニタリング/開始することもできます。</t>
+  </si>
+  <si>
+    <t>範囲：導入編 N7201A442J28(202002) p213「6.3 サービスコントローラー」全文</t>
+  </si>
+  <si>
+    <t>結論：原票からの改変なし</t>
+  </si>
+  <si>
+    <t>頁飾り(「PanaCIM-EE」「導入編」「Page 6-9」「EJS3BJ-MB-06B-03」)と図像(アイコン・罫点グリフU+F0B7)は引用から除外</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果：一致(空白・改行・図像グリフを除き文字列同一)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7. 異常時の対応(仮) / 7-5 PanaCIMサービスの起動・停止・再起動(仮実装・未承認)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出典：PanaCIM-EE 取扱説明書「導入編 N7201A442J28(202002)」p213「6.3 サービスコントローラー」。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取扱注意：引用範囲に認証情報・個人情報は含まれない(2026-10-23 確認済み)。手順2の「アイコン」の後と手順3の各文頭には、原文でアイコン・罫点の図像が入る(文字として抽出されないため引用外)。</t>
+  </si>
+  <si>
+    <t>所在：09_佐藤さん引継ぎ\佐藤(勇)\Pana-CIM 説明書</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2023,7 +2083,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2151,116 +2211,21 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2302,6 +2267,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1"/>
@@ -2314,6 +2288,107 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2343,6 +2418,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -10434,102 +10512,102 @@
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="27"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="92"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="108"/>
       <c r="W1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="93" t="s">
+      <c r="X1" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="Y1" s="94"/>
+      <c r="Y1" s="102"/>
     </row>
     <row r="2" spans="1:25" ht="58.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="30"/>
       <c r="B2" s="31"/>
-      <c r="D2" s="95" t="s">
+      <c r="D2" s="103" t="s">
         <v>299</v>
       </c>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
-      <c r="S2" s="96"/>
-      <c r="T2" s="96"/>
-      <c r="U2" s="96"/>
-      <c r="V2" s="96"/>
-      <c r="W2" s="96"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="104"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="104"/>
+      <c r="V2" s="104"/>
+      <c r="W2" s="104"/>
       <c r="X2" s="32"/>
       <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
       <c r="B3" s="34"/>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="105" t="s">
         <v>300</v>
       </c>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="97"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="97"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="97"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="105"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="105"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
+      <c r="T3" s="105"/>
+      <c r="U3" s="105"/>
+      <c r="V3" s="105"/>
+      <c r="W3" s="105"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="35"/>
     </row>
     <row r="4" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
       <c r="B4" s="34"/>
-      <c r="D4" s="97" t="s">
+      <c r="D4" s="105" t="s">
         <v>301</v>
       </c>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="97"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="97"/>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="97"/>
-      <c r="S4" s="97"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="97"/>
-      <c r="V4" s="97"/>
-      <c r="W4" s="97"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="105"/>
+      <c r="P4" s="105"/>
+      <c r="Q4" s="105"/>
+      <c r="R4" s="105"/>
+      <c r="S4" s="105"/>
+      <c r="T4" s="105"/>
+      <c r="U4" s="105"/>
+      <c r="V4" s="105"/>
+      <c r="W4" s="105"/>
       <c r="X4" s="34"/>
       <c r="Y4" s="35"/>
     </row>
@@ -10573,21 +10651,21 @@
       <c r="K6" s="34"/>
       <c r="L6" s="37"/>
       <c r="M6" s="37"/>
-      <c r="O6" s="90" t="s">
+      <c r="O6" s="106" t="s">
         <v>302</v>
       </c>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="92"/>
-      <c r="R6" s="90" t="s">
+      <c r="P6" s="107"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="106" t="s">
         <v>303</v>
       </c>
-      <c r="S6" s="91"/>
-      <c r="T6" s="92"/>
-      <c r="U6" s="90" t="s">
+      <c r="S6" s="107"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="106" t="s">
         <v>304</v>
       </c>
-      <c r="V6" s="91"/>
-      <c r="W6" s="92"/>
+      <c r="V6" s="107"/>
+      <c r="W6" s="108"/>
       <c r="Y6" s="35"/>
     </row>
     <row r="7" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10604,15 +10682,15 @@
       <c r="K7" s="34"/>
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="81"/>
-      <c r="V7" s="82"/>
-      <c r="W7" s="83"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="111"/>
+      <c r="R7" s="109"/>
+      <c r="S7" s="110"/>
+      <c r="T7" s="111"/>
+      <c r="U7" s="109"/>
+      <c r="V7" s="110"/>
+      <c r="W7" s="111"/>
       <c r="Y7" s="35"/>
     </row>
     <row r="8" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10629,15 +10707,15 @@
       <c r="K8" s="34"/>
       <c r="L8" s="37"/>
       <c r="M8" s="37"/>
-      <c r="O8" s="84"/>
-      <c r="P8" s="85"/>
-      <c r="Q8" s="86"/>
-      <c r="R8" s="84"/>
-      <c r="S8" s="85"/>
-      <c r="T8" s="86"/>
-      <c r="U8" s="84"/>
-      <c r="V8" s="85"/>
-      <c r="W8" s="86"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="114"/>
+      <c r="R8" s="112"/>
+      <c r="S8" s="113"/>
+      <c r="T8" s="114"/>
+      <c r="U8" s="112"/>
+      <c r="V8" s="113"/>
+      <c r="W8" s="114"/>
       <c r="Y8" s="35"/>
     </row>
     <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10681,18 +10759,18 @@
       <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="N10" s="37"/>
-      <c r="P10" s="87" t="s">
+      <c r="P10" s="115" t="s">
         <v>305</v>
       </c>
-      <c r="Q10" s="87"/>
-      <c r="R10" s="87"/>
-      <c r="S10" s="88" t="s">
+      <c r="Q10" s="115"/>
+      <c r="R10" s="115"/>
+      <c r="S10" s="116" t="s">
         <v>306</v>
       </c>
-      <c r="T10" s="88"/>
-      <c r="U10" s="88"/>
-      <c r="V10" s="88"/>
-      <c r="W10" s="88"/>
+      <c r="T10" s="116"/>
+      <c r="U10" s="116"/>
+      <c r="V10" s="116"/>
+      <c r="W10" s="116"/>
       <c r="Y10" s="35"/>
     </row>
     <row r="11" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10710,27 +10788,27 @@
       <c r="L11" s="37"/>
       <c r="M11" s="37"/>
       <c r="N11" s="37"/>
-      <c r="P11" s="80" t="s">
+      <c r="P11" s="99" t="s">
         <v>307</v>
       </c>
-      <c r="Q11" s="80"/>
-      <c r="R11" s="80"/>
-      <c r="S11" s="89" t="s">
+      <c r="Q11" s="99"/>
+      <c r="R11" s="99"/>
+      <c r="S11" s="117" t="s">
         <v>306</v>
       </c>
-      <c r="T11" s="89"/>
-      <c r="U11" s="89"/>
-      <c r="V11" s="89"/>
-      <c r="W11" s="89"/>
+      <c r="T11" s="117"/>
+      <c r="U11" s="117"/>
+      <c r="V11" s="117"/>
+      <c r="W11" s="117"/>
       <c r="Y11" s="35"/>
     </row>
     <row r="12" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="38"/>
-      <c r="P12" s="80" t="s">
+      <c r="P12" s="99" t="s">
         <v>308</v>
       </c>
-      <c r="Q12" s="80"/>
-      <c r="R12" s="80"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="99"/>
       <c r="S12" s="39"/>
       <c r="T12" s="39"/>
       <c r="U12" s="40" t="s">
@@ -10752,642 +10830,642 @@
         <v>311</v>
       </c>
       <c r="B14" s="45"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="99"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="98"/>
       <c r="K14" s="100"/>
-      <c r="L14" s="101"/>
-      <c r="M14" s="101"/>
-      <c r="N14" s="101"/>
-      <c r="O14" s="101"/>
-      <c r="P14" s="101"/>
-      <c r="Q14" s="102"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="99"/>
-      <c r="T14" s="98"/>
-      <c r="U14" s="80"/>
-      <c r="V14" s="80"/>
-      <c r="W14" s="99"/>
-      <c r="X14" s="98"/>
-      <c r="Y14" s="99"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="95"/>
+      <c r="P14" s="95"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="97"/>
+      <c r="S14" s="98"/>
+      <c r="T14" s="97"/>
+      <c r="U14" s="99"/>
+      <c r="V14" s="99"/>
+      <c r="W14" s="98"/>
+      <c r="X14" s="97"/>
+      <c r="Y14" s="98"/>
     </row>
     <row r="15" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B15" s="45"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="99"/>
+      <c r="C15" s="97"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="97"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="98"/>
       <c r="K15" s="100"/>
-      <c r="L15" s="101"/>
-      <c r="M15" s="101"/>
-      <c r="N15" s="101"/>
-      <c r="O15" s="101"/>
-      <c r="P15" s="101"/>
-      <c r="Q15" s="102"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="99"/>
-      <c r="T15" s="98"/>
-      <c r="U15" s="80"/>
-      <c r="V15" s="80"/>
-      <c r="W15" s="99"/>
-      <c r="X15" s="98"/>
-      <c r="Y15" s="99"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="95"/>
+      <c r="P15" s="95"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="97"/>
+      <c r="S15" s="98"/>
+      <c r="T15" s="97"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="99"/>
+      <c r="W15" s="98"/>
+      <c r="X15" s="97"/>
+      <c r="Y15" s="98"/>
     </row>
     <row r="16" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B16" s="45"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="99"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="98"/>
       <c r="K16" s="100"/>
-      <c r="L16" s="101"/>
-      <c r="M16" s="101"/>
-      <c r="N16" s="101"/>
-      <c r="O16" s="101"/>
-      <c r="P16" s="101"/>
-      <c r="Q16" s="102"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="99"/>
-      <c r="T16" s="98"/>
-      <c r="U16" s="80"/>
-      <c r="V16" s="80"/>
-      <c r="W16" s="99"/>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="99"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="95"/>
+      <c r="P16" s="95"/>
+      <c r="Q16" s="96"/>
+      <c r="R16" s="97"/>
+      <c r="S16" s="98"/>
+      <c r="T16" s="97"/>
+      <c r="U16" s="99"/>
+      <c r="V16" s="99"/>
+      <c r="W16" s="98"/>
+      <c r="X16" s="97"/>
+      <c r="Y16" s="98"/>
     </row>
     <row r="17" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B17" s="45"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="99"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="98"/>
       <c r="K17" s="100"/>
-      <c r="L17" s="101"/>
-      <c r="M17" s="101"/>
-      <c r="N17" s="101"/>
-      <c r="O17" s="101"/>
-      <c r="P17" s="101"/>
-      <c r="Q17" s="102"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="99"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="80"/>
-      <c r="V17" s="80"/>
-      <c r="W17" s="99"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="99"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="95"/>
+      <c r="P17" s="95"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="97"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="97"/>
+      <c r="U17" s="99"/>
+      <c r="V17" s="99"/>
+      <c r="W17" s="98"/>
+      <c r="X17" s="97"/>
+      <c r="Y17" s="98"/>
     </row>
     <row r="18" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B18" s="45"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="99"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="99"/>
+      <c r="I18" s="99"/>
+      <c r="J18" s="98"/>
       <c r="K18" s="100"/>
-      <c r="L18" s="101"/>
-      <c r="M18" s="101"/>
-      <c r="N18" s="101"/>
-      <c r="O18" s="101"/>
-      <c r="P18" s="101"/>
-      <c r="Q18" s="102"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="99"/>
-      <c r="T18" s="98"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="80"/>
-      <c r="W18" s="99"/>
-      <c r="X18" s="98"/>
-      <c r="Y18" s="99"/>
+      <c r="L18" s="95"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="95"/>
+      <c r="P18" s="95"/>
+      <c r="Q18" s="96"/>
+      <c r="R18" s="97"/>
+      <c r="S18" s="98"/>
+      <c r="T18" s="97"/>
+      <c r="U18" s="99"/>
+      <c r="V18" s="99"/>
+      <c r="W18" s="98"/>
+      <c r="X18" s="97"/>
+      <c r="Y18" s="98"/>
     </row>
     <row r="19" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B19" s="45"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="99"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
+      <c r="J19" s="98"/>
       <c r="K19" s="100"/>
-      <c r="L19" s="101"/>
-      <c r="M19" s="101"/>
-      <c r="N19" s="101"/>
-      <c r="O19" s="101"/>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="102"/>
-      <c r="R19" s="98"/>
-      <c r="S19" s="99"/>
-      <c r="T19" s="98"/>
-      <c r="U19" s="80"/>
-      <c r="V19" s="80"/>
-      <c r="W19" s="99"/>
-      <c r="X19" s="98"/>
-      <c r="Y19" s="99"/>
+      <c r="L19" s="95"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="95"/>
+      <c r="P19" s="95"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="97"/>
+      <c r="S19" s="98"/>
+      <c r="T19" s="97"/>
+      <c r="U19" s="99"/>
+      <c r="V19" s="99"/>
+      <c r="W19" s="98"/>
+      <c r="X19" s="97"/>
+      <c r="Y19" s="98"/>
     </row>
     <row r="20" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B20" s="45"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="99"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="99"/>
+      <c r="J20" s="98"/>
       <c r="K20" s="100"/>
-      <c r="L20" s="101"/>
-      <c r="M20" s="101"/>
-      <c r="N20" s="101"/>
-      <c r="O20" s="101"/>
-      <c r="P20" s="101"/>
-      <c r="Q20" s="102"/>
-      <c r="R20" s="98"/>
-      <c r="S20" s="99"/>
-      <c r="T20" s="98"/>
-      <c r="U20" s="80"/>
-      <c r="V20" s="80"/>
-      <c r="W20" s="99"/>
-      <c r="X20" s="98"/>
-      <c r="Y20" s="99"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="95"/>
+      <c r="P20" s="95"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="97"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="97"/>
+      <c r="U20" s="99"/>
+      <c r="V20" s="99"/>
+      <c r="W20" s="98"/>
+      <c r="X20" s="97"/>
+      <c r="Y20" s="98"/>
     </row>
     <row r="21" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B21" s="45"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="99"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="99"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="98"/>
       <c r="K21" s="100"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="101"/>
-      <c r="N21" s="101"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="101"/>
-      <c r="Q21" s="102"/>
-      <c r="R21" s="98"/>
-      <c r="S21" s="99"/>
-      <c r="T21" s="98"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="80"/>
-      <c r="W21" s="99"/>
-      <c r="X21" s="98"/>
-      <c r="Y21" s="99"/>
+      <c r="L21" s="95"/>
+      <c r="M21" s="95"/>
+      <c r="N21" s="95"/>
+      <c r="O21" s="95"/>
+      <c r="P21" s="95"/>
+      <c r="Q21" s="96"/>
+      <c r="R21" s="97"/>
+      <c r="S21" s="98"/>
+      <c r="T21" s="97"/>
+      <c r="U21" s="99"/>
+      <c r="V21" s="99"/>
+      <c r="W21" s="98"/>
+      <c r="X21" s="97"/>
+      <c r="Y21" s="98"/>
     </row>
     <row r="22" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B22" s="45"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="99"/>
+      <c r="C22" s="97"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="99"/>
+      <c r="I22" s="99"/>
+      <c r="J22" s="98"/>
       <c r="K22" s="100"/>
-      <c r="L22" s="101"/>
-      <c r="M22" s="101"/>
-      <c r="N22" s="101"/>
-      <c r="O22" s="101"/>
-      <c r="P22" s="101"/>
-      <c r="Q22" s="102"/>
-      <c r="R22" s="98"/>
-      <c r="S22" s="99"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="80"/>
-      <c r="V22" s="80"/>
-      <c r="W22" s="99"/>
-      <c r="X22" s="98"/>
-      <c r="Y22" s="99"/>
+      <c r="L22" s="95"/>
+      <c r="M22" s="95"/>
+      <c r="N22" s="95"/>
+      <c r="O22" s="95"/>
+      <c r="P22" s="95"/>
+      <c r="Q22" s="96"/>
+      <c r="R22" s="97"/>
+      <c r="S22" s="98"/>
+      <c r="T22" s="97"/>
+      <c r="U22" s="99"/>
+      <c r="V22" s="99"/>
+      <c r="W22" s="98"/>
+      <c r="X22" s="97"/>
+      <c r="Y22" s="98"/>
     </row>
     <row r="23" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B23" s="45"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="99"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="97"/>
+      <c r="H23" s="99"/>
+      <c r="I23" s="99"/>
+      <c r="J23" s="98"/>
       <c r="K23" s="100"/>
-      <c r="L23" s="101"/>
-      <c r="M23" s="101"/>
-      <c r="N23" s="101"/>
-      <c r="O23" s="101"/>
-      <c r="P23" s="101"/>
-      <c r="Q23" s="102"/>
-      <c r="R23" s="98"/>
-      <c r="S23" s="99"/>
-      <c r="T23" s="98"/>
-      <c r="U23" s="80"/>
-      <c r="V23" s="80"/>
-      <c r="W23" s="99"/>
-      <c r="X23" s="98"/>
-      <c r="Y23" s="99"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="95"/>
+      <c r="O23" s="95"/>
+      <c r="P23" s="95"/>
+      <c r="Q23" s="96"/>
+      <c r="R23" s="97"/>
+      <c r="S23" s="98"/>
+      <c r="T23" s="97"/>
+      <c r="U23" s="99"/>
+      <c r="V23" s="99"/>
+      <c r="W23" s="98"/>
+      <c r="X23" s="97"/>
+      <c r="Y23" s="98"/>
     </row>
     <row r="24" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B24" s="45"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="99"/>
+      <c r="C24" s="97"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="98"/>
       <c r="K24" s="100"/>
-      <c r="L24" s="101"/>
-      <c r="M24" s="101"/>
-      <c r="N24" s="101"/>
-      <c r="O24" s="101"/>
-      <c r="P24" s="101"/>
-      <c r="Q24" s="102"/>
-      <c r="R24" s="98"/>
-      <c r="S24" s="99"/>
-      <c r="T24" s="98"/>
-      <c r="U24" s="80"/>
-      <c r="V24" s="80"/>
-      <c r="W24" s="99"/>
-      <c r="X24" s="98"/>
-      <c r="Y24" s="99"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="95"/>
+      <c r="O24" s="95"/>
+      <c r="P24" s="95"/>
+      <c r="Q24" s="96"/>
+      <c r="R24" s="97"/>
+      <c r="S24" s="98"/>
+      <c r="T24" s="97"/>
+      <c r="U24" s="99"/>
+      <c r="V24" s="99"/>
+      <c r="W24" s="98"/>
+      <c r="X24" s="97"/>
+      <c r="Y24" s="98"/>
     </row>
     <row r="25" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B25" s="45"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="99"/>
+      <c r="C25" s="97"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="98"/>
       <c r="K25" s="100"/>
-      <c r="L25" s="101"/>
-      <c r="M25" s="101"/>
-      <c r="N25" s="101"/>
-      <c r="O25" s="101"/>
-      <c r="P25" s="101"/>
-      <c r="Q25" s="102"/>
-      <c r="R25" s="98"/>
-      <c r="S25" s="99"/>
-      <c r="T25" s="98"/>
-      <c r="U25" s="80"/>
-      <c r="V25" s="80"/>
-      <c r="W25" s="99"/>
-      <c r="X25" s="98"/>
-      <c r="Y25" s="99"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="95"/>
+      <c r="O25" s="95"/>
+      <c r="P25" s="95"/>
+      <c r="Q25" s="96"/>
+      <c r="R25" s="97"/>
+      <c r="S25" s="98"/>
+      <c r="T25" s="97"/>
+      <c r="U25" s="99"/>
+      <c r="V25" s="99"/>
+      <c r="W25" s="98"/>
+      <c r="X25" s="97"/>
+      <c r="Y25" s="98"/>
     </row>
     <row r="26" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B26" s="45"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="98"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="99"/>
+      <c r="C26" s="97"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="97"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="98"/>
       <c r="K26" s="100"/>
-      <c r="L26" s="101"/>
-      <c r="M26" s="101"/>
-      <c r="N26" s="101"/>
-      <c r="O26" s="101"/>
-      <c r="P26" s="101"/>
-      <c r="Q26" s="102"/>
-      <c r="R26" s="98"/>
-      <c r="S26" s="99"/>
-      <c r="T26" s="98"/>
-      <c r="U26" s="80"/>
-      <c r="V26" s="80"/>
-      <c r="W26" s="99"/>
-      <c r="X26" s="98"/>
-      <c r="Y26" s="99"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="95"/>
+      <c r="O26" s="95"/>
+      <c r="P26" s="95"/>
+      <c r="Q26" s="96"/>
+      <c r="R26" s="97"/>
+      <c r="S26" s="98"/>
+      <c r="T26" s="97"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="99"/>
+      <c r="W26" s="98"/>
+      <c r="X26" s="97"/>
+      <c r="Y26" s="98"/>
     </row>
     <row r="27" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B27" s="45"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="80"/>
-      <c r="I27" s="80"/>
-      <c r="J27" s="99"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="99"/>
+      <c r="I27" s="99"/>
+      <c r="J27" s="98"/>
       <c r="K27" s="100"/>
-      <c r="L27" s="101"/>
-      <c r="M27" s="101"/>
-      <c r="N27" s="101"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="101"/>
-      <c r="Q27" s="102"/>
-      <c r="R27" s="98"/>
-      <c r="S27" s="99"/>
-      <c r="T27" s="98"/>
-      <c r="U27" s="80"/>
-      <c r="V27" s="80"/>
-      <c r="W27" s="99"/>
-      <c r="X27" s="98"/>
-      <c r="Y27" s="99"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="95"/>
+      <c r="Q27" s="96"/>
+      <c r="R27" s="97"/>
+      <c r="S27" s="98"/>
+      <c r="T27" s="97"/>
+      <c r="U27" s="99"/>
+      <c r="V27" s="99"/>
+      <c r="W27" s="98"/>
+      <c r="X27" s="97"/>
+      <c r="Y27" s="98"/>
     </row>
     <row r="28" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B28" s="45"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="98"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="99"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="99"/>
+      <c r="I28" s="99"/>
+      <c r="J28" s="98"/>
       <c r="K28" s="100"/>
-      <c r="L28" s="101"/>
-      <c r="M28" s="101"/>
-      <c r="N28" s="101"/>
-      <c r="O28" s="101"/>
-      <c r="P28" s="101"/>
-      <c r="Q28" s="102"/>
-      <c r="R28" s="98"/>
-      <c r="S28" s="99"/>
-      <c r="T28" s="98"/>
-      <c r="U28" s="80"/>
-      <c r="V28" s="80"/>
-      <c r="W28" s="99"/>
-      <c r="X28" s="98"/>
-      <c r="Y28" s="99"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="95"/>
+      <c r="O28" s="95"/>
+      <c r="P28" s="95"/>
+      <c r="Q28" s="96"/>
+      <c r="R28" s="97"/>
+      <c r="S28" s="98"/>
+      <c r="T28" s="97"/>
+      <c r="U28" s="99"/>
+      <c r="V28" s="99"/>
+      <c r="W28" s="98"/>
+      <c r="X28" s="97"/>
+      <c r="Y28" s="98"/>
     </row>
     <row r="29" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B29" s="45"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="99"/>
-      <c r="G29" s="98"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="99"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="97"/>
+      <c r="H29" s="99"/>
+      <c r="I29" s="99"/>
+      <c r="J29" s="98"/>
       <c r="K29" s="100"/>
-      <c r="L29" s="101"/>
-      <c r="M29" s="101"/>
-      <c r="N29" s="101"/>
-      <c r="O29" s="101"/>
-      <c r="P29" s="101"/>
-      <c r="Q29" s="102"/>
-      <c r="R29" s="98"/>
-      <c r="S29" s="99"/>
-      <c r="T29" s="98"/>
-      <c r="U29" s="80"/>
-      <c r="V29" s="80"/>
-      <c r="W29" s="99"/>
-      <c r="X29" s="98"/>
-      <c r="Y29" s="99"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="95"/>
+      <c r="N29" s="95"/>
+      <c r="O29" s="95"/>
+      <c r="P29" s="95"/>
+      <c r="Q29" s="96"/>
+      <c r="R29" s="97"/>
+      <c r="S29" s="98"/>
+      <c r="T29" s="97"/>
+      <c r="U29" s="99"/>
+      <c r="V29" s="99"/>
+      <c r="W29" s="98"/>
+      <c r="X29" s="97"/>
+      <c r="Y29" s="98"/>
     </row>
     <row r="30" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
         <v>311</v>
       </c>
       <c r="B30" s="45"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="99"/>
-      <c r="G30" s="98"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="99"/>
+      <c r="C30" s="97"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="99"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="98"/>
       <c r="K30" s="100"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="101"/>
-      <c r="N30" s="101"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="101"/>
-      <c r="Q30" s="102"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="99"/>
-      <c r="T30" s="98"/>
-      <c r="U30" s="80"/>
-      <c r="V30" s="80"/>
-      <c r="W30" s="99"/>
-      <c r="X30" s="98"/>
-      <c r="Y30" s="99"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="96"/>
+      <c r="R30" s="97"/>
+      <c r="S30" s="98"/>
+      <c r="T30" s="97"/>
+      <c r="U30" s="99"/>
+      <c r="V30" s="99"/>
+      <c r="W30" s="98"/>
+      <c r="X30" s="97"/>
+      <c r="Y30" s="98"/>
     </row>
     <row r="31" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="44"/>
       <c r="B31" s="45"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="105"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="85"/>
+      <c r="H31" s="86"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="87"/>
       <c r="K31" s="100"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="101"/>
-      <c r="N31" s="101"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="101"/>
-      <c r="Q31" s="102"/>
-      <c r="R31" s="98"/>
-      <c r="S31" s="99"/>
-      <c r="T31" s="98"/>
-      <c r="U31" s="80"/>
-      <c r="V31" s="80"/>
-      <c r="W31" s="99"/>
-      <c r="X31" s="98"/>
-      <c r="Y31" s="99"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="95"/>
+      <c r="P31" s="95"/>
+      <c r="Q31" s="96"/>
+      <c r="R31" s="97"/>
+      <c r="S31" s="98"/>
+      <c r="T31" s="97"/>
+      <c r="U31" s="99"/>
+      <c r="V31" s="99"/>
+      <c r="W31" s="98"/>
+      <c r="X31" s="97"/>
+      <c r="Y31" s="98"/>
     </row>
     <row r="32" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="45"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="105"/>
-      <c r="K32" s="106"/>
-      <c r="L32" s="101"/>
-      <c r="M32" s="101"/>
-      <c r="N32" s="101"/>
-      <c r="O32" s="101"/>
-      <c r="P32" s="101"/>
-      <c r="Q32" s="102"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="99"/>
-      <c r="T32" s="98"/>
-      <c r="U32" s="80"/>
-      <c r="V32" s="80"/>
-      <c r="W32" s="99"/>
-      <c r="X32" s="98"/>
-      <c r="Y32" s="99"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="85"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="87"/>
+      <c r="K32" s="94"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="95"/>
+      <c r="O32" s="95"/>
+      <c r="P32" s="95"/>
+      <c r="Q32" s="96"/>
+      <c r="R32" s="97"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="97"/>
+      <c r="U32" s="99"/>
+      <c r="V32" s="99"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="97"/>
+      <c r="Y32" s="98"/>
     </row>
     <row r="33" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="46"/>
       <c r="B33" s="47"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="103"/>
-      <c r="H33" s="104"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="105"/>
-      <c r="K33" s="124"/>
-      <c r="L33" s="125"/>
-      <c r="M33" s="125"/>
-      <c r="N33" s="125"/>
-      <c r="O33" s="125"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="126"/>
-      <c r="R33" s="127"/>
-      <c r="S33" s="128"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="129"/>
-      <c r="V33" s="129"/>
-      <c r="W33" s="128"/>
-      <c r="X33" s="127"/>
-      <c r="Y33" s="128"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="88"/>
+      <c r="L33" s="89"/>
+      <c r="M33" s="89"/>
+      <c r="N33" s="89"/>
+      <c r="O33" s="89"/>
+      <c r="P33" s="89"/>
+      <c r="Q33" s="90"/>
+      <c r="R33" s="91"/>
+      <c r="S33" s="92"/>
+      <c r="T33" s="91"/>
+      <c r="U33" s="93"/>
+      <c r="V33" s="93"/>
+      <c r="W33" s="92"/>
+      <c r="X33" s="91"/>
+      <c r="Y33" s="92"/>
     </row>
     <row r="34" spans="1:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="107" t="s">
+      <c r="A34" s="68" t="s">
         <v>312</v>
       </c>
-      <c r="B34" s="108"/>
-      <c r="C34" s="111" t="s">
+      <c r="B34" s="69"/>
+      <c r="C34" s="72" t="s">
         <v>313</v>
       </c>
-      <c r="D34" s="112"/>
-      <c r="E34" s="112"/>
-      <c r="F34" s="113"/>
-      <c r="G34" s="111" t="s">
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="72" t="s">
         <v>314</v>
       </c>
-      <c r="H34" s="112"/>
-      <c r="I34" s="112"/>
-      <c r="J34" s="113"/>
-      <c r="K34" s="107" t="s">
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="68" t="s">
         <v>315</v>
       </c>
-      <c r="L34" s="117"/>
-      <c r="M34" s="117"/>
-      <c r="N34" s="117"/>
-      <c r="O34" s="117"/>
-      <c r="P34" s="117"/>
-      <c r="Q34" s="118"/>
-      <c r="R34" s="107" t="s">
+      <c r="L34" s="78"/>
+      <c r="M34" s="78"/>
+      <c r="N34" s="78"/>
+      <c r="O34" s="78"/>
+      <c r="P34" s="78"/>
+      <c r="Q34" s="79"/>
+      <c r="R34" s="68" t="s">
         <v>316</v>
       </c>
-      <c r="S34" s="108"/>
-      <c r="T34" s="107" t="s">
+      <c r="S34" s="69"/>
+      <c r="T34" s="68" t="s">
         <v>317</v>
       </c>
-      <c r="U34" s="122"/>
-      <c r="V34" s="122"/>
-      <c r="W34" s="108"/>
-      <c r="X34" s="107" t="s">
+      <c r="U34" s="83"/>
+      <c r="V34" s="83"/>
+      <c r="W34" s="69"/>
+      <c r="X34" s="68" t="s">
         <v>318</v>
       </c>
-      <c r="Y34" s="108"/>
+      <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A35" s="109"/>
-      <c r="B35" s="110"/>
-      <c r="C35" s="114"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="114"/>
-      <c r="H35" s="115"/>
-      <c r="I35" s="115"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="119"/>
-      <c r="L35" s="120"/>
-      <c r="M35" s="120"/>
-      <c r="N35" s="120"/>
-      <c r="O35" s="120"/>
-      <c r="P35" s="120"/>
-      <c r="Q35" s="121"/>
-      <c r="R35" s="109"/>
-      <c r="S35" s="110"/>
-      <c r="T35" s="109"/>
-      <c r="U35" s="123"/>
-      <c r="V35" s="123"/>
-      <c r="W35" s="110"/>
-      <c r="X35" s="109"/>
-      <c r="Y35" s="110"/>
+      <c r="A35" s="70"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="81"/>
+      <c r="M35" s="81"/>
+      <c r="N35" s="81"/>
+      <c r="O35" s="81"/>
+      <c r="P35" s="81"/>
+      <c r="Q35" s="82"/>
+      <c r="R35" s="70"/>
+      <c r="S35" s="71"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="84"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="71"/>
+      <c r="X35" s="70"/>
+      <c r="Y35" s="71"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="s">
@@ -11402,116 +11480,15 @@
     </row>
   </sheetData>
   <mergeCells count="143">
-    <mergeCell ref="X34:Y35"/>
-    <mergeCell ref="A34:B35"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G34:J35"/>
-    <mergeCell ref="K34:Q35"/>
-    <mergeCell ref="R34:S35"/>
-    <mergeCell ref="T34:W35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="K33:Q33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="T33:W33"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="T32:W32"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:W31"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="T30:W30"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:W29"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:W28"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:W27"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="X25:Y25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:W23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:W22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="O7:Q8"/>
+    <mergeCell ref="R7:T8"/>
+    <mergeCell ref="U7:W8"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="S10:W10"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="P1:V1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="D2:W2"/>
     <mergeCell ref="D3:W3"/>
@@ -11536,15 +11513,116 @@
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="K14:Q14"/>
     <mergeCell ref="R14:S14"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="O7:Q8"/>
-    <mergeCell ref="R7:T8"/>
-    <mergeCell ref="U7:W8"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="S10:W10"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:W22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:W23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="T26:W26"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:W28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:W27"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="T30:W30"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:W29"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="T32:W32"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:W31"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X34:Y35"/>
+    <mergeCell ref="A34:B35"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G34:J35"/>
+    <mergeCell ref="K34:Q35"/>
+    <mergeCell ref="R34:S35"/>
+    <mergeCell ref="T34:W35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="K33:Q33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="T33:W33"/>
+    <mergeCell ref="X33:Y33"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.86614173228346458" right="0.51181102362204722" top="0.59055118110236227" bottom="0.19685039370078741" header="0.59055118110236227" footer="0.19685039370078741"/>
@@ -11568,206 +11646,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
         <v>228</v>
       </c>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="67"/>
-      <c r="AM4" s="67"/>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -12111,206 +12189,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="67"/>
-      <c r="AM4" s="67"/>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
@@ -13306,206 +13384,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
         <v>230</v>
       </c>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="67"/>
-      <c r="AM4" s="67"/>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
@@ -13763,206 +13841,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
         <v>231</v>
       </c>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="67"/>
-      <c r="AM4" s="67"/>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -14253,172 +14331,104 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ59"/>
-  <sheetFormatPr defaultColWidth="1.88671875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225D337B-374B-485E-837D-9DD4AC44325E}">
+  <dimension ref="A1:AZ24"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="51" width="1.88671875" style="1" customWidth="1"/>
-    <col min="52" max="52" width="3.33203125" style="1" customWidth="1"/>
-    <col min="53" max="53" width="1.88671875" style="1" customWidth="1"/>
-    <col min="54" max="16384" width="1.88671875" style="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="52" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+    <row r="1" spans="1:52" ht="5.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-    </row>
-    <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
-        <v>2</v>
-      </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
+    </row>
+    <row r="2" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="66"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
-    </row>
-    <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="67" t="s">
+        <v>367</v>
+      </c>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+    </row>
+    <row r="4" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
-        <v>220</v>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="67" t="s">
+        <v>368</v>
       </c>
       <c r="H4" s="67"/>
       <c r="I4" s="67"/>
@@ -14464,7 +14474,334 @@
       <c r="AW4" s="67"/>
       <c r="AX4" s="67"/>
       <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="AZ4" s="67"/>
+    </row>
+    <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="64" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C7" s="63" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C8" s="63" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="9" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C9" s="145" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C10" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="11" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="64" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="12" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C12" s="63" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="13" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="15" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="63">
+        <v>1</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="16" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="63">
+        <v>2</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="63">
+        <v>3</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C18" s="63" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="20" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="64" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C21" s="63" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C22" s="63" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C23" s="63" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C24" s="63" t="s">
+        <v>378</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A1:V2"/>
+    <mergeCell ref="G3:V3"/>
+    <mergeCell ref="G4:AZ4"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AZ59"/>
+  <sheetFormatPr defaultColWidth="1.88671875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="51" width="1.88671875" style="1" customWidth="1"/>
+    <col min="52" max="52" width="3.33203125" style="1" customWidth="1"/>
+    <col min="53" max="53" width="1.88671875" style="1" customWidth="1"/>
+    <col min="54" max="16384" width="1.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="128" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+    </row>
+    <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
+        <v>2</v>
+      </c>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
+    </row>
+    <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="124" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
+    </row>
+    <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="132" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
+        <v>220</v>
+      </c>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="11" t="s">
@@ -14648,206 +14985,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="135"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="77"/>
-      <c r="AA2" s="77"/>
-      <c r="AB2" s="77"/>
-      <c r="AC2" s="131"/>
-      <c r="AD2" s="131"/>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="131"/>
-      <c r="AG2" s="131"/>
-      <c r="AH2" s="131"/>
-      <c r="AI2" s="131"/>
-      <c r="AJ2" s="131"/>
-      <c r="AK2" s="131"/>
-      <c r="AL2" s="131"/>
-      <c r="AM2" s="131"/>
-      <c r="AN2" s="131"/>
-      <c r="AO2" s="131"/>
-      <c r="AP2" s="131"/>
-      <c r="AQ2" s="131"/>
-      <c r="AR2" s="131"/>
-      <c r="AS2" s="131"/>
-      <c r="AT2" s="74"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="131"/>
+      <c r="Y2" s="131"/>
+      <c r="Z2" s="131"/>
+      <c r="AA2" s="131"/>
+      <c r="AB2" s="131"/>
+      <c r="AC2" s="136"/>
+      <c r="AD2" s="136"/>
+      <c r="AE2" s="136"/>
+      <c r="AF2" s="136"/>
+      <c r="AG2" s="136"/>
+      <c r="AH2" s="136"/>
+      <c r="AI2" s="136"/>
+      <c r="AJ2" s="136"/>
+      <c r="AK2" s="136"/>
+      <c r="AL2" s="136"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="136"/>
+      <c r="AO2" s="136"/>
+      <c r="AP2" s="136"/>
+      <c r="AQ2" s="136"/>
+      <c r="AR2" s="136"/>
+      <c r="AS2" s="136"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="AV2" s="77"/>
-      <c r="AW2" s="130"/>
-      <c r="AX2" s="131"/>
-      <c r="AY2" s="131"/>
-      <c r="AZ2" s="132"/>
+      <c r="AV2" s="131"/>
+      <c r="AW2" s="135"/>
+      <c r="AX2" s="136"/>
+      <c r="AY2" s="136"/>
+      <c r="AZ2" s="137"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="139" t="s">
+      <c r="A3" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="130"/>
+      <c r="S3" s="130"/>
+      <c r="T3" s="130"/>
+      <c r="U3" s="130"/>
+      <c r="V3" s="130"/>
+      <c r="W3" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="X3" s="69"/>
-      <c r="Y3" s="69"/>
-      <c r="Z3" s="69"/>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="69"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="118"/>
+      <c r="Y3" s="118"/>
+      <c r="Z3" s="118"/>
+      <c r="AA3" s="118"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="AD3" s="69"/>
-      <c r="AE3" s="69"/>
-      <c r="AF3" s="69"/>
-      <c r="AG3" s="69"/>
-      <c r="AH3" s="69"/>
-      <c r="AI3" s="69"/>
-      <c r="AJ3" s="69"/>
-      <c r="AK3" s="69"/>
-      <c r="AL3" s="69"/>
-      <c r="AM3" s="69"/>
-      <c r="AN3" s="69"/>
-      <c r="AO3" s="69"/>
-      <c r="AP3" s="69"/>
-      <c r="AQ3" s="69"/>
-      <c r="AR3" s="69"/>
-      <c r="AS3" s="69"/>
-      <c r="AT3" s="69"/>
-      <c r="AU3" s="69"/>
-      <c r="AV3" s="69"/>
-      <c r="AW3" s="69"/>
-      <c r="AX3" s="69"/>
-      <c r="AY3" s="69"/>
-      <c r="AZ3" s="134"/>
+      <c r="AD3" s="118"/>
+      <c r="AE3" s="118"/>
+      <c r="AF3" s="118"/>
+      <c r="AG3" s="118"/>
+      <c r="AH3" s="118"/>
+      <c r="AI3" s="118"/>
+      <c r="AJ3" s="118"/>
+      <c r="AK3" s="118"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
+      <c r="AQ3" s="118"/>
+      <c r="AR3" s="118"/>
+      <c r="AS3" s="118"/>
+      <c r="AT3" s="118"/>
+      <c r="AU3" s="118"/>
+      <c r="AV3" s="118"/>
+      <c r="AW3" s="118"/>
+      <c r="AX3" s="118"/>
+      <c r="AY3" s="118"/>
+      <c r="AZ3" s="139"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="141" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="121" t="s">
         <v>221</v>
       </c>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="66"/>
-      <c r="X4" s="66"/>
-      <c r="Y4" s="66"/>
-      <c r="Z4" s="66"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
-      <c r="AM4" s="66"/>
-      <c r="AN4" s="66"/>
-      <c r="AO4" s="66"/>
-      <c r="AP4" s="66"/>
-      <c r="AQ4" s="66"/>
-      <c r="AR4" s="66"/>
-      <c r="AS4" s="66"/>
-      <c r="AT4" s="66"/>
-      <c r="AU4" s="66"/>
-      <c r="AV4" s="66"/>
-      <c r="AW4" s="66"/>
-      <c r="AX4" s="66"/>
-      <c r="AY4" s="66"/>
-      <c r="AZ4" s="133"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="121"/>
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="121"/>
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="121"/>
+      <c r="AQ4" s="121"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="121"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="121"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="121"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="121"/>
+      <c r="AZ4" s="138"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -14958,206 +15295,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="135"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="77"/>
-      <c r="AA2" s="77"/>
-      <c r="AB2" s="77"/>
-      <c r="AC2" s="131"/>
-      <c r="AD2" s="131"/>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="131"/>
-      <c r="AG2" s="131"/>
-      <c r="AH2" s="131"/>
-      <c r="AI2" s="131"/>
-      <c r="AJ2" s="131"/>
-      <c r="AK2" s="131"/>
-      <c r="AL2" s="131"/>
-      <c r="AM2" s="131"/>
-      <c r="AN2" s="131"/>
-      <c r="AO2" s="131"/>
-      <c r="AP2" s="131"/>
-      <c r="AQ2" s="131"/>
-      <c r="AR2" s="131"/>
-      <c r="AS2" s="131"/>
-      <c r="AT2" s="74"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="131"/>
+      <c r="Y2" s="131"/>
+      <c r="Z2" s="131"/>
+      <c r="AA2" s="131"/>
+      <c r="AB2" s="131"/>
+      <c r="AC2" s="136"/>
+      <c r="AD2" s="136"/>
+      <c r="AE2" s="136"/>
+      <c r="AF2" s="136"/>
+      <c r="AG2" s="136"/>
+      <c r="AH2" s="136"/>
+      <c r="AI2" s="136"/>
+      <c r="AJ2" s="136"/>
+      <c r="AK2" s="136"/>
+      <c r="AL2" s="136"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="136"/>
+      <c r="AO2" s="136"/>
+      <c r="AP2" s="136"/>
+      <c r="AQ2" s="136"/>
+      <c r="AR2" s="136"/>
+      <c r="AS2" s="136"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="AV2" s="77"/>
-      <c r="AW2" s="130"/>
-      <c r="AX2" s="131"/>
-      <c r="AY2" s="131"/>
-      <c r="AZ2" s="132"/>
+      <c r="AV2" s="131"/>
+      <c r="AW2" s="135"/>
+      <c r="AX2" s="136"/>
+      <c r="AY2" s="136"/>
+      <c r="AZ2" s="137"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="139" t="s">
+      <c r="A3" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="130"/>
+      <c r="S3" s="130"/>
+      <c r="T3" s="130"/>
+      <c r="U3" s="130"/>
+      <c r="V3" s="130"/>
+      <c r="W3" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="X3" s="69"/>
-      <c r="Y3" s="69"/>
-      <c r="Z3" s="69"/>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="69"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="118"/>
+      <c r="Y3" s="118"/>
+      <c r="Z3" s="118"/>
+      <c r="AA3" s="118"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="AD3" s="69"/>
-      <c r="AE3" s="69"/>
-      <c r="AF3" s="69"/>
-      <c r="AG3" s="69"/>
-      <c r="AH3" s="69"/>
-      <c r="AI3" s="69"/>
-      <c r="AJ3" s="69"/>
-      <c r="AK3" s="69"/>
-      <c r="AL3" s="69"/>
-      <c r="AM3" s="69"/>
-      <c r="AN3" s="69"/>
-      <c r="AO3" s="69"/>
-      <c r="AP3" s="69"/>
-      <c r="AQ3" s="69"/>
-      <c r="AR3" s="69"/>
-      <c r="AS3" s="69"/>
-      <c r="AT3" s="69"/>
-      <c r="AU3" s="69"/>
-      <c r="AV3" s="69"/>
-      <c r="AW3" s="69"/>
-      <c r="AX3" s="69"/>
-      <c r="AY3" s="69"/>
-      <c r="AZ3" s="134"/>
+      <c r="AD3" s="118"/>
+      <c r="AE3" s="118"/>
+      <c r="AF3" s="118"/>
+      <c r="AG3" s="118"/>
+      <c r="AH3" s="118"/>
+      <c r="AI3" s="118"/>
+      <c r="AJ3" s="118"/>
+      <c r="AK3" s="118"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
+      <c r="AQ3" s="118"/>
+      <c r="AR3" s="118"/>
+      <c r="AS3" s="118"/>
+      <c r="AT3" s="118"/>
+      <c r="AU3" s="118"/>
+      <c r="AV3" s="118"/>
+      <c r="AW3" s="118"/>
+      <c r="AX3" s="118"/>
+      <c r="AY3" s="118"/>
+      <c r="AZ3" s="139"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="141" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="121" t="s">
         <v>222</v>
       </c>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="66"/>
-      <c r="X4" s="66"/>
-      <c r="Y4" s="66"/>
-      <c r="Z4" s="66"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
-      <c r="AM4" s="66"/>
-      <c r="AN4" s="66"/>
-      <c r="AO4" s="66"/>
-      <c r="AP4" s="66"/>
-      <c r="AQ4" s="66"/>
-      <c r="AR4" s="66"/>
-      <c r="AS4" s="66"/>
-      <c r="AT4" s="66"/>
-      <c r="AU4" s="66"/>
-      <c r="AV4" s="66"/>
-      <c r="AW4" s="66"/>
-      <c r="AX4" s="66"/>
-      <c r="AY4" s="66"/>
-      <c r="AZ4" s="133"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="121"/>
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="121"/>
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="121"/>
+      <c r="AQ4" s="121"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="121"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="121"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="121"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="121"/>
+      <c r="AZ4" s="138"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -15272,206 +15609,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="135"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="135"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="135"/>
-      <c r="R2" s="135"/>
-      <c r="S2" s="135"/>
-      <c r="T2" s="135"/>
-      <c r="U2" s="135"/>
-      <c r="V2" s="135"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="77"/>
-      <c r="AA2" s="77"/>
-      <c r="AB2" s="77"/>
-      <c r="AC2" s="131"/>
-      <c r="AD2" s="131"/>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="131"/>
-      <c r="AG2" s="131"/>
-      <c r="AH2" s="131"/>
-      <c r="AI2" s="131"/>
-      <c r="AJ2" s="131"/>
-      <c r="AK2" s="131"/>
-      <c r="AL2" s="131"/>
-      <c r="AM2" s="131"/>
-      <c r="AN2" s="131"/>
-      <c r="AO2" s="131"/>
-      <c r="AP2" s="131"/>
-      <c r="AQ2" s="131"/>
-      <c r="AR2" s="131"/>
-      <c r="AS2" s="131"/>
-      <c r="AT2" s="74"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="131"/>
+      <c r="Y2" s="131"/>
+      <c r="Z2" s="131"/>
+      <c r="AA2" s="131"/>
+      <c r="AB2" s="131"/>
+      <c r="AC2" s="136"/>
+      <c r="AD2" s="136"/>
+      <c r="AE2" s="136"/>
+      <c r="AF2" s="136"/>
+      <c r="AG2" s="136"/>
+      <c r="AH2" s="136"/>
+      <c r="AI2" s="136"/>
+      <c r="AJ2" s="136"/>
+      <c r="AK2" s="136"/>
+      <c r="AL2" s="136"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="136"/>
+      <c r="AO2" s="136"/>
+      <c r="AP2" s="136"/>
+      <c r="AQ2" s="136"/>
+      <c r="AR2" s="136"/>
+      <c r="AS2" s="136"/>
+      <c r="AT2" s="127"/>
+      <c r="AU2" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="AV2" s="77"/>
-      <c r="AW2" s="130"/>
-      <c r="AX2" s="131"/>
-      <c r="AY2" s="131"/>
-      <c r="AZ2" s="132"/>
+      <c r="AV2" s="131"/>
+      <c r="AW2" s="135"/>
+      <c r="AX2" s="136"/>
+      <c r="AY2" s="136"/>
+      <c r="AZ2" s="137"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="139" t="s">
+      <c r="A3" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="130"/>
+      <c r="S3" s="130"/>
+      <c r="T3" s="130"/>
+      <c r="U3" s="130"/>
+      <c r="V3" s="130"/>
+      <c r="W3" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="X3" s="69"/>
-      <c r="Y3" s="69"/>
-      <c r="Z3" s="69"/>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="69"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="118"/>
+      <c r="Y3" s="118"/>
+      <c r="Z3" s="118"/>
+      <c r="AA3" s="118"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="AD3" s="69"/>
-      <c r="AE3" s="69"/>
-      <c r="AF3" s="69"/>
-      <c r="AG3" s="69"/>
-      <c r="AH3" s="69"/>
-      <c r="AI3" s="69"/>
-      <c r="AJ3" s="69"/>
-      <c r="AK3" s="69"/>
-      <c r="AL3" s="69"/>
-      <c r="AM3" s="69"/>
-      <c r="AN3" s="69"/>
-      <c r="AO3" s="69"/>
-      <c r="AP3" s="69"/>
-      <c r="AQ3" s="69"/>
-      <c r="AR3" s="69"/>
-      <c r="AS3" s="69"/>
-      <c r="AT3" s="69"/>
-      <c r="AU3" s="69"/>
-      <c r="AV3" s="69"/>
-      <c r="AW3" s="69"/>
-      <c r="AX3" s="69"/>
-      <c r="AY3" s="69"/>
-      <c r="AZ3" s="134"/>
+      <c r="AD3" s="118"/>
+      <c r="AE3" s="118"/>
+      <c r="AF3" s="118"/>
+      <c r="AG3" s="118"/>
+      <c r="AH3" s="118"/>
+      <c r="AI3" s="118"/>
+      <c r="AJ3" s="118"/>
+      <c r="AK3" s="118"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
+      <c r="AQ3" s="118"/>
+      <c r="AR3" s="118"/>
+      <c r="AS3" s="118"/>
+      <c r="AT3" s="118"/>
+      <c r="AU3" s="118"/>
+      <c r="AV3" s="118"/>
+      <c r="AW3" s="118"/>
+      <c r="AX3" s="118"/>
+      <c r="AY3" s="118"/>
+      <c r="AZ3" s="139"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="141" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="121" t="s">
         <v>223</v>
       </c>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="66"/>
-      <c r="X4" s="66"/>
-      <c r="Y4" s="66"/>
-      <c r="Z4" s="66"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
-      <c r="AM4" s="66"/>
-      <c r="AN4" s="66"/>
-      <c r="AO4" s="66"/>
-      <c r="AP4" s="66"/>
-      <c r="AQ4" s="66"/>
-      <c r="AR4" s="66"/>
-      <c r="AS4" s="66"/>
-      <c r="AT4" s="66"/>
-      <c r="AU4" s="66"/>
-      <c r="AV4" s="66"/>
-      <c r="AW4" s="66"/>
-      <c r="AX4" s="66"/>
-      <c r="AY4" s="66"/>
-      <c r="AZ4" s="133"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="121"/>
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="121"/>
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="121"/>
+      <c r="AQ4" s="121"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="121"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="121"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="121"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="121"/>
+      <c r="AZ4" s="138"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -15581,206 +15918,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
         <v>224</v>
       </c>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="67"/>
-      <c r="AM4" s="67"/>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="18" t="s">
@@ -16147,206 +16484,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
         <v>225</v>
       </c>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="67"/>
-      <c r="AM4" s="67"/>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -16500,206 +16837,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
         <v>226</v>
       </c>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="67"/>
-      <c r="AM4" s="67"/>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -17160,206 +17497,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
     </row>
     <row r="2" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="79" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="75"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="64"/>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64"/>
-      <c r="AG2" s="64"/>
-      <c r="AH2" s="64"/>
-      <c r="AI2" s="64"/>
-      <c r="AJ2" s="64"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="64"/>
-      <c r="AM2" s="64"/>
-      <c r="AN2" s="64"/>
-      <c r="AO2" s="64"/>
-      <c r="AP2" s="64"/>
-      <c r="AQ2" s="64"/>
-      <c r="AR2" s="64"/>
-      <c r="AS2" s="64"/>
-      <c r="AT2" s="75"/>
-      <c r="AU2" s="77" t="s">
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="125"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="125"/>
+      <c r="AO2" s="125"/>
+      <c r="AP2" s="125"/>
+      <c r="AQ2" s="125"/>
+      <c r="AR2" s="125"/>
+      <c r="AS2" s="125"/>
+      <c r="AT2" s="126"/>
+      <c r="AU2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="AV2" s="75"/>
-      <c r="AW2" s="63"/>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="64"/>
-      <c r="AZ2" s="65"/>
+      <c r="AV2" s="126"/>
+      <c r="AW2" s="133"/>
+      <c r="AX2" s="125"/>
+      <c r="AY2" s="125"/>
+      <c r="AZ2" s="134"/>
     </row>
     <row r="3" spans="1:52" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="69" t="s">
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="126"/>
+      <c r="W3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="70"/>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="69" t="s">
+      <c r="X3" s="119"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="120"/>
+      <c r="AC3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="70"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="70"/>
-      <c r="AJ3" s="70"/>
-      <c r="AK3" s="70"/>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
-      <c r="AN3" s="70"/>
-      <c r="AO3" s="70"/>
-      <c r="AP3" s="70"/>
-      <c r="AQ3" s="70"/>
-      <c r="AR3" s="70"/>
-      <c r="AS3" s="70"/>
-      <c r="AT3" s="70"/>
-      <c r="AU3" s="70"/>
-      <c r="AV3" s="70"/>
-      <c r="AW3" s="70"/>
-      <c r="AX3" s="70"/>
-      <c r="AY3" s="70"/>
-      <c r="AZ3" s="71"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="120"/>
     </row>
     <row r="4" spans="1:52" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="66" t="s">
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="121" t="s">
         <v>227</v>
       </c>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="67"/>
-      <c r="AI4" s="67"/>
-      <c r="AJ4" s="67"/>
-      <c r="AK4" s="67"/>
-      <c r="AL4" s="67"/>
-      <c r="AM4" s="67"/>
-      <c r="AN4" s="67"/>
-      <c r="AO4" s="67"/>
-      <c r="AP4" s="67"/>
-      <c r="AQ4" s="67"/>
-      <c r="AR4" s="67"/>
-      <c r="AS4" s="67"/>
-      <c r="AT4" s="67"/>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="67"/>
-      <c r="AW4" s="67"/>
-      <c r="AX4" s="67"/>
-      <c r="AY4" s="67"/>
-      <c r="AZ4" s="68"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="122"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="123"/>
     </row>
     <row r="6" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nk365-my.sharepoint.com/personal/ss80751_ad_nkc_co_jp/Documents/ドキュメント/Work_Vault/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{FC963946-1E0E-4B79-95BF-70F924E5A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{142EF00D-26A8-425C-8E6F-AD76DF28B65E}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{FC963946-1E0E-4B79-95BF-70F924E5A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0BA3DFE-1660-4BA0-8790-9AEF5E45B834}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2307,79 +2307,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2421,6 +2348,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1"/>
@@ -2431,6 +2367,70 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -6840,7 +6840,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="50800" tIns="25400" rIns="25400" bIns="12700" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="50800" tIns="25400" rIns="76200" bIns="12700" rtlCol="0" anchor="t" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
@@ -8870,23 +8870,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>27940</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>93980</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>123190</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>73660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>27940</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>123190</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>40640</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="rel_e1">
+        <xdr:cNvPr id="36" name="rel_e1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2850ADF-FD0D-97EA-06D8-A26E8F3D67B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F6901AA-A9DA-BDFC-53E4-71776537A18E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8894,7 +8894,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2489200" y="4292600"/>
+          <a:off x="1936750" y="2832100"/>
           <a:ext cx="0" cy="927100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -8926,23 +8926,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>104140</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>104140</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>48260</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="rel_l_e1">
+        <xdr:cNvPr id="37" name="rel_l_e1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4B0F193-3457-4325-2915-1B4C67AAAABD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07A99C3F-12DD-3CE6-8E61-796A0BE467F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8950,7 +8950,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2565400" y="4622800"/>
+          <a:off x="2006600" y="3175000"/>
           <a:ext cx="762000" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8995,7 +8995,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="25400" tIns="12700" rIns="25400" bIns="12700" rtlCol="0" anchor="ctr" anchorCtr="0">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -9017,23 +9017,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>43180</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2540</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>81280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>58420</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>2540</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>17780</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66040</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="22" name="rel_e2">
+        <xdr:cNvPr id="38" name="rel_e2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE217655-CD63-6CB7-8C4F-9A6532A8720E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C5FBE70-8E4B-4A72-65FF-3A7E64B954E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9041,8 +9041,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="3670300" y="4140200"/>
-          <a:ext cx="533400" cy="1181100"/>
+          <a:off x="3111500" y="2679700"/>
+          <a:ext cx="533400" cy="1104900"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9073,23 +9073,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>55880</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>73660</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="rel_l_e2">
+        <xdr:cNvPr id="39" name="rel_l_e2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C01D4FF0-9F45-B05F-0F62-CBC080E4AE57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BA18AEC-BB7C-D11C-AD28-04FB53CDBACD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9097,7 +9097,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3683000" y="4432300"/>
+          <a:off x="2819400" y="3175000"/>
           <a:ext cx="508000" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9142,7 +9142,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="25400" tIns="12700" rIns="25400" bIns="12700" rtlCol="0" anchor="ctr" anchorCtr="0">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -9164,23 +9164,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>43180</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2540</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>58420</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>2540</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>17780</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>142240</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="24" name="rel_e3">
+        <xdr:cNvPr id="40" name="rel_e3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1436841-314E-BF4F-BC25-D125024A9600}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF970C1F-DF23-5FEA-4AA2-0DEFD9394FEC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9188,8 +9188,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3670300" y="5778500"/>
-          <a:ext cx="533400" cy="1943100"/>
+          <a:off x="3111500" y="4343400"/>
+          <a:ext cx="533400" cy="1917700"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9220,23 +9220,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>33020</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>78740</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>35560</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="rel_l_e3">
+        <xdr:cNvPr id="41" name="rel_l_e3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60F62E0E-EF84-0F0F-45F7-BE10BEF158E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9300E934-830B-8227-EAE7-53236006A5CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9244,7 +9244,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3048000" y="7112000"/>
+          <a:off x="2540000" y="5651500"/>
           <a:ext cx="863600" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9289,7 +9289,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="25400" tIns="12700" rIns="25400" bIns="12700" rtlCol="0" anchor="ctr" anchorCtr="0">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -9331,23 +9331,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>104140</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>17780</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="26" name="rel_e4">
+        <xdr:cNvPr id="42" name="rel_e4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB8C8DD0-55BF-4AE0-2B96-606599F6FE35}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56BEDDD3-3835-5931-681F-9501C7732038}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9355,8 +9355,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1917700" y="6769100"/>
-          <a:ext cx="76200" cy="2108200"/>
+          <a:off x="1358900" y="5308600"/>
+          <a:ext cx="127000" cy="2108200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9387,23 +9387,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>48260</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>5080</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>116840</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>86360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="rel_l_e4">
+        <xdr:cNvPr id="43" name="rel_l_e4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4508E444-571B-CBE5-02D4-3E9217E0F49A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D566860-9E4D-D00B-0109-68179D28E7EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9411,7 +9411,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1473200" y="8204200"/>
+          <a:off x="914400" y="6705600"/>
           <a:ext cx="457200" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9456,7 +9456,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="25400" tIns="12700" rIns="25400" bIns="12700" rtlCol="0" anchor="ctr" anchorCtr="0">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -9488,23 +9488,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>5080</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>48260</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>17780</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="28" name="rel_e5">
+        <xdr:cNvPr id="44" name="rel_e5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB481082-0371-F60B-A655-149618EC505E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF801179-819E-A973-1962-50026FC0440A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9512,8 +9512,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="2984500" y="6769100"/>
-          <a:ext cx="431800" cy="2108200"/>
+          <a:off x="2476500" y="5308600"/>
+          <a:ext cx="381000" cy="2108200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9544,23 +9544,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>58420</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>5080</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>78740</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>124460</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="rel_l_e5">
+        <xdr:cNvPr id="45" name="rel_l_e5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F171470F-AE66-2A7C-1CA0-11A731D3DE1A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B836D3F-BA66-03BB-5E7E-FB8D0AED04AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9568,7 +9568,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3556000" y="8204200"/>
+          <a:off x="3048000" y="6743700"/>
           <a:ext cx="279400" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9613,7 +9613,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="25400" tIns="12700" rIns="25400" bIns="12700" rtlCol="0" anchor="ctr" anchorCtr="0">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -9635,23 +9635,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>43180</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2540</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>96520</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>55880</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>119380</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="rel_e6">
+        <xdr:cNvPr id="46" name="rel_e6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{318B81CC-2CFA-2E04-8A78-652BD8E1D5B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9B81A42-DD1F-DB1B-B0B6-8324AA591372}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9659,8 +9659,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="3670300" y="5702300"/>
-          <a:ext cx="1219200" cy="76200"/>
+          <a:off x="3111500" y="4191000"/>
+          <a:ext cx="1219200" cy="127000"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9691,23 +9691,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>43180</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>104140</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="rel_l_e6">
+        <xdr:cNvPr id="47" name="rel_l_e6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9144FE7-ABEE-AD58-AB56-29356920639C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8BE994C-545B-4030-935C-B2355A4F6491}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9715,7 +9715,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4318000" y="5562600"/>
+          <a:off x="4597400" y="4064000"/>
           <a:ext cx="558800" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9760,7 +9760,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="25400" tIns="12700" rIns="25400" bIns="12700" rtlCol="0" anchor="ctr" anchorCtr="0">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -9782,23 +9782,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>43180</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2540</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>119380</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="32" name="rel_e7">
+        <xdr:cNvPr id="48" name="rel_e7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D3FB81A-7520-028D-9268-38938EC905CB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{977440CC-382E-A9C0-66A0-1931E7D41FCF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9806,8 +9806,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="3670300" y="5562600"/>
-          <a:ext cx="2679700" cy="215900"/>
+          <a:off x="3111500" y="4038600"/>
+          <a:ext cx="2679700" cy="279400"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9839,22 +9839,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>40</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>20320</xdr:rowOff>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
-      <xdr:colOff>20320</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>81280</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="rel_l_e7">
+        <xdr:cNvPr id="49" name="rel_l_e7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB6C5C45-45FF-6D19-0F0E-B599C2F2FA0A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7671AF1-945B-5FC7-715E-B28256650B7F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9862,7 +9862,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5181600" y="5499100"/>
+          <a:off x="5207000" y="4140200"/>
           <a:ext cx="279400" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9907,7 +9907,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="25400" tIns="12700" rIns="25400" bIns="12700" rtlCol="0" anchor="ctr" anchorCtr="0">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -9929,23 +9929,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>43180</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>2540</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>109220</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>104140</xdr:rowOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>74930</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="34" name="rel_e8">
+        <xdr:cNvPr id="50" name="rel_e8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F9878C6-3183-C118-4B9A-FE526BB5BF56}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{082DE194-746E-7A4E-8FDF-B3AACED62EE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9953,8 +9953,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3670300" y="5168900"/>
-          <a:ext cx="1879600" cy="254000"/>
+          <a:off x="3111500" y="3708400"/>
+          <a:ext cx="1885950" cy="177800"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9985,23 +9985,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>73660</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>154940</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>66040</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>154940</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134620</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="rel_l_e8">
+        <xdr:cNvPr id="51" name="rel_l_e8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E940A58-2F84-D6F3-92FE-F66A8EFB97D0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38B7E5F0-A070-BEE6-9E9D-A937B73175FE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10009,7 +10009,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4597400" y="5334000"/>
+          <a:off x="4089400" y="3873500"/>
           <a:ext cx="1168400" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10054,7 +10054,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="25400" tIns="12700" rIns="25400" bIns="12700" rtlCol="0" anchor="ctr" anchorCtr="0">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" rtlCol="0" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -14096,102 +14096,102 @@
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="27"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="96"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="124"/>
       <c r="W1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="97" t="s">
+      <c r="X1" s="117" t="s">
         <v>297</v>
       </c>
-      <c r="Y1" s="98"/>
+      <c r="Y1" s="118"/>
     </row>
     <row r="2" spans="1:25" ht="58.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="30"/>
       <c r="B2" s="31"/>
-      <c r="D2" s="99" t="s">
+      <c r="D2" s="119" t="s">
         <v>298</v>
       </c>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="100"/>
-      <c r="R2" s="100"/>
-      <c r="S2" s="100"/>
-      <c r="T2" s="100"/>
-      <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="120"/>
+      <c r="T2" s="120"/>
+      <c r="U2" s="120"/>
+      <c r="V2" s="120"/>
+      <c r="W2" s="120"/>
       <c r="X2" s="32"/>
       <c r="Y2" s="24"/>
     </row>
     <row r="3" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
       <c r="B3" s="34"/>
-      <c r="D3" s="101" t="s">
+      <c r="D3" s="121" t="s">
         <v>299</v>
       </c>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="101"/>
-      <c r="T3" s="101"/>
-      <c r="U3" s="101"/>
-      <c r="V3" s="101"/>
-      <c r="W3" s="101"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121"/>
+      <c r="R3" s="121"/>
+      <c r="S3" s="121"/>
+      <c r="T3" s="121"/>
+      <c r="U3" s="121"/>
+      <c r="V3" s="121"/>
+      <c r="W3" s="121"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="35"/>
     </row>
     <row r="4" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
       <c r="B4" s="34"/>
-      <c r="D4" s="101" t="s">
+      <c r="D4" s="121" t="s">
         <v>300</v>
       </c>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="101"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="101"/>
-      <c r="U4" s="101"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="101"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
       <c r="X4" s="34"/>
       <c r="Y4" s="35"/>
     </row>
@@ -14235,21 +14235,21 @@
       <c r="K6" s="34"/>
       <c r="L6" s="37"/>
       <c r="M6" s="37"/>
-      <c r="O6" s="94" t="s">
+      <c r="O6" s="122" t="s">
         <v>301</v>
       </c>
-      <c r="P6" s="95"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="94" t="s">
+      <c r="P6" s="123"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="122" t="s">
         <v>302</v>
       </c>
-      <c r="S6" s="95"/>
-      <c r="T6" s="96"/>
-      <c r="U6" s="94" t="s">
+      <c r="S6" s="123"/>
+      <c r="T6" s="124"/>
+      <c r="U6" s="122" t="s">
         <v>303</v>
       </c>
-      <c r="V6" s="95"/>
-      <c r="W6" s="96"/>
+      <c r="V6" s="123"/>
+      <c r="W6" s="124"/>
       <c r="Y6" s="35"/>
     </row>
     <row r="7" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14266,15 +14266,15 @@
       <c r="K7" s="34"/>
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="86"/>
-      <c r="Q7" s="87"/>
-      <c r="R7" s="85"/>
-      <c r="S7" s="86"/>
-      <c r="T7" s="87"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="86"/>
-      <c r="W7" s="87"/>
+      <c r="O7" s="125"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="125"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="127"/>
+      <c r="U7" s="125"/>
+      <c r="V7" s="126"/>
+      <c r="W7" s="127"/>
       <c r="Y7" s="35"/>
     </row>
     <row r="8" spans="1:25" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -14291,15 +14291,15 @@
       <c r="K8" s="34"/>
       <c r="L8" s="37"/>
       <c r="M8" s="37"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="89"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="88"/>
-      <c r="S8" s="89"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="88"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="90"/>
+      <c r="O8" s="128"/>
+      <c r="P8" s="129"/>
+      <c r="Q8" s="130"/>
+      <c r="R8" s="128"/>
+      <c r="S8" s="129"/>
+      <c r="T8" s="130"/>
+      <c r="U8" s="128"/>
+      <c r="V8" s="129"/>
+      <c r="W8" s="130"/>
       <c r="Y8" s="35"/>
     </row>
     <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -14343,18 +14343,18 @@
       <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="N10" s="37"/>
-      <c r="P10" s="91" t="s">
+      <c r="P10" s="131" t="s">
         <v>304</v>
       </c>
-      <c r="Q10" s="91"/>
-      <c r="R10" s="91"/>
-      <c r="S10" s="92" t="s">
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="132" t="s">
         <v>305</v>
       </c>
-      <c r="T10" s="92"/>
-      <c r="U10" s="92"/>
-      <c r="V10" s="92"/>
-      <c r="W10" s="92"/>
+      <c r="T10" s="132"/>
+      <c r="U10" s="132"/>
+      <c r="V10" s="132"/>
+      <c r="W10" s="132"/>
       <c r="Y10" s="35"/>
     </row>
     <row r="11" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14372,27 +14372,27 @@
       <c r="L11" s="37"/>
       <c r="M11" s="37"/>
       <c r="N11" s="37"/>
-      <c r="P11" s="84" t="s">
+      <c r="P11" s="115" t="s">
         <v>306</v>
       </c>
-      <c r="Q11" s="84"/>
-      <c r="R11" s="84"/>
-      <c r="S11" s="93" t="s">
+      <c r="Q11" s="115"/>
+      <c r="R11" s="115"/>
+      <c r="S11" s="133" t="s">
         <v>305</v>
       </c>
-      <c r="T11" s="93"/>
-      <c r="U11" s="93"/>
-      <c r="V11" s="93"/>
-      <c r="W11" s="93"/>
+      <c r="T11" s="133"/>
+      <c r="U11" s="133"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="133"/>
       <c r="Y11" s="35"/>
     </row>
     <row r="12" spans="1:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="38"/>
-      <c r="P12" s="84" t="s">
+      <c r="P12" s="115" t="s">
         <v>307</v>
       </c>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="84"/>
+      <c r="Q12" s="115"/>
+      <c r="R12" s="115"/>
       <c r="S12" s="39"/>
       <c r="T12" s="39"/>
       <c r="U12" s="40" t="s">
@@ -14414,642 +14414,642 @@
         <v>310</v>
       </c>
       <c r="B14" s="45"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="105"/>
-      <c r="O14" s="105"/>
-      <c r="P14" s="105"/>
-      <c r="Q14" s="106"/>
-      <c r="R14" s="102"/>
-      <c r="S14" s="103"/>
-      <c r="T14" s="102"/>
-      <c r="U14" s="84"/>
-      <c r="V14" s="84"/>
-      <c r="W14" s="103"/>
-      <c r="X14" s="102"/>
-      <c r="Y14" s="103"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="116"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="112"/>
+      <c r="R14" s="113"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="113"/>
+      <c r="U14" s="115"/>
+      <c r="V14" s="115"/>
+      <c r="W14" s="114"/>
+      <c r="X14" s="113"/>
+      <c r="Y14" s="114"/>
     </row>
     <row r="15" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B15" s="45"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="103"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="106"/>
-      <c r="R15" s="102"/>
-      <c r="S15" s="103"/>
-      <c r="T15" s="102"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="103"/>
-      <c r="X15" s="102"/>
-      <c r="Y15" s="103"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="116"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="112"/>
+      <c r="R15" s="113"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="113"/>
+      <c r="U15" s="115"/>
+      <c r="V15" s="115"/>
+      <c r="W15" s="114"/>
+      <c r="X15" s="113"/>
+      <c r="Y15" s="114"/>
     </row>
     <row r="16" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B16" s="45"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="84"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="103"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="105"/>
-      <c r="M16" s="105"/>
-      <c r="N16" s="105"/>
-      <c r="O16" s="105"/>
-      <c r="P16" s="105"/>
-      <c r="Q16" s="106"/>
-      <c r="R16" s="102"/>
-      <c r="S16" s="103"/>
-      <c r="T16" s="102"/>
-      <c r="U16" s="84"/>
-      <c r="V16" s="84"/>
-      <c r="W16" s="103"/>
-      <c r="X16" s="102"/>
-      <c r="Y16" s="103"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="116"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="112"/>
+      <c r="R16" s="113"/>
+      <c r="S16" s="114"/>
+      <c r="T16" s="113"/>
+      <c r="U16" s="115"/>
+      <c r="V16" s="115"/>
+      <c r="W16" s="114"/>
+      <c r="X16" s="113"/>
+      <c r="Y16" s="114"/>
     </row>
     <row r="17" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B17" s="45"/>
-      <c r="C17" s="102"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="103"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="105"/>
-      <c r="M17" s="105"/>
-      <c r="N17" s="105"/>
-      <c r="O17" s="105"/>
-      <c r="P17" s="105"/>
-      <c r="Q17" s="106"/>
-      <c r="R17" s="102"/>
-      <c r="S17" s="103"/>
-      <c r="T17" s="102"/>
-      <c r="U17" s="84"/>
-      <c r="V17" s="84"/>
-      <c r="W17" s="103"/>
-      <c r="X17" s="102"/>
-      <c r="Y17" s="103"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="116"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="111"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="111"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="112"/>
+      <c r="R17" s="113"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="113"/>
+      <c r="U17" s="115"/>
+      <c r="V17" s="115"/>
+      <c r="W17" s="114"/>
+      <c r="X17" s="113"/>
+      <c r="Y17" s="114"/>
     </row>
     <row r="18" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B18" s="45"/>
-      <c r="C18" s="102"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="105"/>
-      <c r="M18" s="105"/>
-      <c r="N18" s="105"/>
-      <c r="O18" s="105"/>
-      <c r="P18" s="105"/>
-      <c r="Q18" s="106"/>
-      <c r="R18" s="102"/>
-      <c r="S18" s="103"/>
-      <c r="T18" s="102"/>
-      <c r="U18" s="84"/>
-      <c r="V18" s="84"/>
-      <c r="W18" s="103"/>
-      <c r="X18" s="102"/>
-      <c r="Y18" s="103"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="116"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="113"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="113"/>
+      <c r="U18" s="115"/>
+      <c r="V18" s="115"/>
+      <c r="W18" s="114"/>
+      <c r="X18" s="113"/>
+      <c r="Y18" s="114"/>
     </row>
     <row r="19" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B19" s="45"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="104"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="105"/>
-      <c r="N19" s="105"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="105"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="102"/>
-      <c r="S19" s="103"/>
-      <c r="T19" s="102"/>
-      <c r="U19" s="84"/>
-      <c r="V19" s="84"/>
-      <c r="W19" s="103"/>
-      <c r="X19" s="102"/>
-      <c r="Y19" s="103"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="116"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="111"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="111"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="112"/>
+      <c r="R19" s="113"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="113"/>
+      <c r="U19" s="115"/>
+      <c r="V19" s="115"/>
+      <c r="W19" s="114"/>
+      <c r="X19" s="113"/>
+      <c r="Y19" s="114"/>
     </row>
     <row r="20" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B20" s="45"/>
-      <c r="C20" s="102"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="103"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="106"/>
-      <c r="R20" s="102"/>
-      <c r="S20" s="103"/>
-      <c r="T20" s="102"/>
-      <c r="U20" s="84"/>
-      <c r="V20" s="84"/>
-      <c r="W20" s="103"/>
-      <c r="X20" s="102"/>
-      <c r="Y20" s="103"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="114"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="112"/>
+      <c r="R20" s="113"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="113"/>
+      <c r="U20" s="115"/>
+      <c r="V20" s="115"/>
+      <c r="W20" s="114"/>
+      <c r="X20" s="113"/>
+      <c r="Y20" s="114"/>
     </row>
     <row r="21" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B21" s="45"/>
-      <c r="C21" s="102"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="105"/>
-      <c r="M21" s="105"/>
-      <c r="N21" s="105"/>
-      <c r="O21" s="105"/>
-      <c r="P21" s="105"/>
-      <c r="Q21" s="106"/>
-      <c r="R21" s="102"/>
-      <c r="S21" s="103"/>
-      <c r="T21" s="102"/>
-      <c r="U21" s="84"/>
-      <c r="V21" s="84"/>
-      <c r="W21" s="103"/>
-      <c r="X21" s="102"/>
-      <c r="Y21" s="103"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="111"/>
+      <c r="N21" s="111"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="114"/>
+      <c r="T21" s="113"/>
+      <c r="U21" s="115"/>
+      <c r="V21" s="115"/>
+      <c r="W21" s="114"/>
+      <c r="X21" s="113"/>
+      <c r="Y21" s="114"/>
     </row>
     <row r="22" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B22" s="45"/>
-      <c r="C22" s="102"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="105"/>
-      <c r="M22" s="105"/>
-      <c r="N22" s="105"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="105"/>
-      <c r="Q22" s="106"/>
-      <c r="R22" s="102"/>
-      <c r="S22" s="103"/>
-      <c r="T22" s="102"/>
-      <c r="U22" s="84"/>
-      <c r="V22" s="84"/>
-      <c r="W22" s="103"/>
-      <c r="X22" s="102"/>
-      <c r="Y22" s="103"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="112"/>
+      <c r="R22" s="113"/>
+      <c r="S22" s="114"/>
+      <c r="T22" s="113"/>
+      <c r="U22" s="115"/>
+      <c r="V22" s="115"/>
+      <c r="W22" s="114"/>
+      <c r="X22" s="113"/>
+      <c r="Y22" s="114"/>
     </row>
     <row r="23" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B23" s="45"/>
-      <c r="C23" s="102"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="102"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="103"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="105"/>
-      <c r="M23" s="105"/>
-      <c r="N23" s="105"/>
-      <c r="O23" s="105"/>
-      <c r="P23" s="105"/>
-      <c r="Q23" s="106"/>
-      <c r="R23" s="102"/>
-      <c r="S23" s="103"/>
-      <c r="T23" s="102"/>
-      <c r="U23" s="84"/>
-      <c r="V23" s="84"/>
-      <c r="W23" s="103"/>
-      <c r="X23" s="102"/>
-      <c r="Y23" s="103"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="114"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="116"/>
+      <c r="L23" s="111"/>
+      <c r="M23" s="111"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="111"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="112"/>
+      <c r="R23" s="113"/>
+      <c r="S23" s="114"/>
+      <c r="T23" s="113"/>
+      <c r="U23" s="115"/>
+      <c r="V23" s="115"/>
+      <c r="W23" s="114"/>
+      <c r="X23" s="113"/>
+      <c r="Y23" s="114"/>
     </row>
     <row r="24" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B24" s="45"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="105"/>
-      <c r="P24" s="105"/>
-      <c r="Q24" s="106"/>
-      <c r="R24" s="102"/>
-      <c r="S24" s="103"/>
-      <c r="T24" s="102"/>
-      <c r="U24" s="84"/>
-      <c r="V24" s="84"/>
-      <c r="W24" s="103"/>
-      <c r="X24" s="102"/>
-      <c r="Y24" s="103"/>
+      <c r="C24" s="113"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="114"/>
+      <c r="G24" s="113"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="116"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="111"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="112"/>
+      <c r="R24" s="113"/>
+      <c r="S24" s="114"/>
+      <c r="T24" s="113"/>
+      <c r="U24" s="115"/>
+      <c r="V24" s="115"/>
+      <c r="W24" s="114"/>
+      <c r="X24" s="113"/>
+      <c r="Y24" s="114"/>
     </row>
     <row r="25" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B25" s="45"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="105"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="105"/>
-      <c r="Q25" s="106"/>
-      <c r="R25" s="102"/>
-      <c r="S25" s="103"/>
-      <c r="T25" s="102"/>
-      <c r="U25" s="84"/>
-      <c r="V25" s="84"/>
-      <c r="W25" s="103"/>
-      <c r="X25" s="102"/>
-      <c r="Y25" s="103"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="114"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="116"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="111"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="112"/>
+      <c r="R25" s="113"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="113"/>
+      <c r="U25" s="115"/>
+      <c r="V25" s="115"/>
+      <c r="W25" s="114"/>
+      <c r="X25" s="113"/>
+      <c r="Y25" s="114"/>
     </row>
     <row r="26" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B26" s="45"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="84"/>
-      <c r="I26" s="84"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="104"/>
-      <c r="L26" s="105"/>
-      <c r="M26" s="105"/>
-      <c r="N26" s="105"/>
-      <c r="O26" s="105"/>
-      <c r="P26" s="105"/>
-      <c r="Q26" s="106"/>
-      <c r="R26" s="102"/>
-      <c r="S26" s="103"/>
-      <c r="T26" s="102"/>
-      <c r="U26" s="84"/>
-      <c r="V26" s="84"/>
-      <c r="W26" s="103"/>
-      <c r="X26" s="102"/>
-      <c r="Y26" s="103"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="115"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="111"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="111"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="112"/>
+      <c r="R26" s="113"/>
+      <c r="S26" s="114"/>
+      <c r="T26" s="113"/>
+      <c r="U26" s="115"/>
+      <c r="V26" s="115"/>
+      <c r="W26" s="114"/>
+      <c r="X26" s="113"/>
+      <c r="Y26" s="114"/>
     </row>
     <row r="27" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B27" s="45"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="105"/>
-      <c r="M27" s="105"/>
-      <c r="N27" s="105"/>
-      <c r="O27" s="105"/>
-      <c r="P27" s="105"/>
-      <c r="Q27" s="106"/>
-      <c r="R27" s="102"/>
-      <c r="S27" s="103"/>
-      <c r="T27" s="102"/>
-      <c r="U27" s="84"/>
-      <c r="V27" s="84"/>
-      <c r="W27" s="103"/>
-      <c r="X27" s="102"/>
-      <c r="Y27" s="103"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="116"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="111"/>
+      <c r="N27" s="111"/>
+      <c r="O27" s="111"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="112"/>
+      <c r="R27" s="113"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="113"/>
+      <c r="U27" s="115"/>
+      <c r="V27" s="115"/>
+      <c r="W27" s="114"/>
+      <c r="X27" s="113"/>
+      <c r="Y27" s="114"/>
     </row>
     <row r="28" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B28" s="45"/>
-      <c r="C28" s="102"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="103"/>
-      <c r="G28" s="102"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="84"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="105"/>
-      <c r="M28" s="105"/>
-      <c r="N28" s="105"/>
-      <c r="O28" s="105"/>
-      <c r="P28" s="105"/>
-      <c r="Q28" s="106"/>
-      <c r="R28" s="102"/>
-      <c r="S28" s="103"/>
-      <c r="T28" s="102"/>
-      <c r="U28" s="84"/>
-      <c r="V28" s="84"/>
-      <c r="W28" s="103"/>
-      <c r="X28" s="102"/>
-      <c r="Y28" s="103"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="116"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="111"/>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="112"/>
+      <c r="R28" s="113"/>
+      <c r="S28" s="114"/>
+      <c r="T28" s="113"/>
+      <c r="U28" s="115"/>
+      <c r="V28" s="115"/>
+      <c r="W28" s="114"/>
+      <c r="X28" s="113"/>
+      <c r="Y28" s="114"/>
     </row>
     <row r="29" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B29" s="45"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="103"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="105"/>
-      <c r="M29" s="105"/>
-      <c r="N29" s="105"/>
-      <c r="O29" s="105"/>
-      <c r="P29" s="105"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="102"/>
-      <c r="S29" s="103"/>
-      <c r="T29" s="102"/>
-      <c r="U29" s="84"/>
-      <c r="V29" s="84"/>
-      <c r="W29" s="103"/>
-      <c r="X29" s="102"/>
-      <c r="Y29" s="103"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="114"/>
+      <c r="G29" s="113"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="116"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="111"/>
+      <c r="N29" s="111"/>
+      <c r="O29" s="111"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="112"/>
+      <c r="R29" s="113"/>
+      <c r="S29" s="114"/>
+      <c r="T29" s="113"/>
+      <c r="U29" s="115"/>
+      <c r="V29" s="115"/>
+      <c r="W29" s="114"/>
+      <c r="X29" s="113"/>
+      <c r="Y29" s="114"/>
     </row>
     <row r="30" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
         <v>310</v>
       </c>
       <c r="B30" s="45"/>
-      <c r="C30" s="102"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="103"/>
-      <c r="G30" s="102"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="103"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="105"/>
-      <c r="M30" s="105"/>
-      <c r="N30" s="105"/>
-      <c r="O30" s="105"/>
-      <c r="P30" s="105"/>
-      <c r="Q30" s="106"/>
-      <c r="R30" s="102"/>
-      <c r="S30" s="103"/>
-      <c r="T30" s="102"/>
-      <c r="U30" s="84"/>
-      <c r="V30" s="84"/>
-      <c r="W30" s="103"/>
-      <c r="X30" s="102"/>
-      <c r="Y30" s="103"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="116"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="111"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="111"/>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="112"/>
+      <c r="R30" s="113"/>
+      <c r="S30" s="114"/>
+      <c r="T30" s="113"/>
+      <c r="U30" s="115"/>
+      <c r="V30" s="115"/>
+      <c r="W30" s="114"/>
+      <c r="X30" s="113"/>
+      <c r="Y30" s="114"/>
     </row>
     <row r="31" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="44"/>
       <c r="B31" s="45"/>
-      <c r="C31" s="107"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="109"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="108"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="109"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="105"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="105"/>
-      <c r="Q31" s="106"/>
-      <c r="R31" s="102"/>
-      <c r="S31" s="103"/>
-      <c r="T31" s="102"/>
-      <c r="U31" s="84"/>
-      <c r="V31" s="84"/>
-      <c r="W31" s="103"/>
-      <c r="X31" s="102"/>
-      <c r="Y31" s="103"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="103"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="102"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="103"/>
+      <c r="K31" s="116"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="111"/>
+      <c r="N31" s="111"/>
+      <c r="O31" s="111"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="113"/>
+      <c r="S31" s="114"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="115"/>
+      <c r="V31" s="115"/>
+      <c r="W31" s="114"/>
+      <c r="X31" s="113"/>
+      <c r="Y31" s="114"/>
     </row>
     <row r="32" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="45"/>
-      <c r="C32" s="107"/>
-      <c r="D32" s="108"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="109"/>
-      <c r="G32" s="107"/>
-      <c r="H32" s="108"/>
-      <c r="I32" s="108"/>
-      <c r="J32" s="109"/>
+      <c r="C32" s="101"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="102"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="103"/>
       <c r="K32" s="110"/>
-      <c r="L32" s="105"/>
-      <c r="M32" s="105"/>
-      <c r="N32" s="105"/>
-      <c r="O32" s="105"/>
-      <c r="P32" s="105"/>
-      <c r="Q32" s="106"/>
-      <c r="R32" s="102"/>
-      <c r="S32" s="103"/>
-      <c r="T32" s="102"/>
-      <c r="U32" s="84"/>
-      <c r="V32" s="84"/>
-      <c r="W32" s="103"/>
-      <c r="X32" s="102"/>
-      <c r="Y32" s="103"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="111"/>
+      <c r="N32" s="111"/>
+      <c r="O32" s="111"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="112"/>
+      <c r="R32" s="113"/>
+      <c r="S32" s="114"/>
+      <c r="T32" s="113"/>
+      <c r="U32" s="115"/>
+      <c r="V32" s="115"/>
+      <c r="W32" s="114"/>
+      <c r="X32" s="113"/>
+      <c r="Y32" s="114"/>
     </row>
     <row r="33" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="46"/>
       <c r="B33" s="47"/>
-      <c r="C33" s="107"/>
-      <c r="D33" s="108"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="107"/>
-      <c r="H33" s="108"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="109"/>
-      <c r="K33" s="128"/>
-      <c r="L33" s="129"/>
-      <c r="M33" s="129"/>
-      <c r="N33" s="129"/>
-      <c r="O33" s="129"/>
-      <c r="P33" s="129"/>
-      <c r="Q33" s="130"/>
-      <c r="R33" s="131"/>
-      <c r="S33" s="132"/>
-      <c r="T33" s="131"/>
-      <c r="U33" s="133"/>
-      <c r="V33" s="133"/>
-      <c r="W33" s="132"/>
-      <c r="X33" s="131"/>
-      <c r="Y33" s="132"/>
+      <c r="C33" s="101"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="103"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="102"/>
+      <c r="J33" s="103"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="105"/>
+      <c r="M33" s="105"/>
+      <c r="N33" s="105"/>
+      <c r="O33" s="105"/>
+      <c r="P33" s="105"/>
+      <c r="Q33" s="106"/>
+      <c r="R33" s="107"/>
+      <c r="S33" s="108"/>
+      <c r="T33" s="107"/>
+      <c r="U33" s="109"/>
+      <c r="V33" s="109"/>
+      <c r="W33" s="108"/>
+      <c r="X33" s="107"/>
+      <c r="Y33" s="108"/>
     </row>
     <row r="34" spans="1:25" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="111" t="s">
+      <c r="A34" s="84" t="s">
         <v>311</v>
       </c>
-      <c r="B34" s="112"/>
-      <c r="C34" s="115" t="s">
+      <c r="B34" s="85"/>
+      <c r="C34" s="88" t="s">
         <v>312</v>
       </c>
-      <c r="D34" s="116"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="115" t="s">
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="88" t="s">
         <v>313</v>
       </c>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="117"/>
-      <c r="K34" s="111" t="s">
+      <c r="H34" s="89"/>
+      <c r="I34" s="89"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="84" t="s">
         <v>314</v>
       </c>
-      <c r="L34" s="121"/>
-      <c r="M34" s="121"/>
-      <c r="N34" s="121"/>
-      <c r="O34" s="121"/>
-      <c r="P34" s="121"/>
-      <c r="Q34" s="122"/>
-      <c r="R34" s="111" t="s">
+      <c r="L34" s="94"/>
+      <c r="M34" s="94"/>
+      <c r="N34" s="94"/>
+      <c r="O34" s="94"/>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="84" t="s">
         <v>315</v>
       </c>
-      <c r="S34" s="112"/>
-      <c r="T34" s="111" t="s">
+      <c r="S34" s="85"/>
+      <c r="T34" s="84" t="s">
         <v>316</v>
       </c>
-      <c r="U34" s="126"/>
-      <c r="V34" s="126"/>
-      <c r="W34" s="112"/>
-      <c r="X34" s="111" t="s">
+      <c r="U34" s="99"/>
+      <c r="V34" s="99"/>
+      <c r="W34" s="85"/>
+      <c r="X34" s="84" t="s">
         <v>317</v>
       </c>
-      <c r="Y34" s="112"/>
+      <c r="Y34" s="85"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A35" s="113"/>
-      <c r="B35" s="114"/>
-      <c r="C35" s="118"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="119"/>
-      <c r="I35" s="119"/>
-      <c r="J35" s="120"/>
-      <c r="K35" s="123"/>
-      <c r="L35" s="124"/>
-      <c r="M35" s="124"/>
-      <c r="N35" s="124"/>
-      <c r="O35" s="124"/>
-      <c r="P35" s="124"/>
-      <c r="Q35" s="125"/>
-      <c r="R35" s="113"/>
-      <c r="S35" s="114"/>
-      <c r="T35" s="113"/>
-      <c r="U35" s="127"/>
-      <c r="V35" s="127"/>
-      <c r="W35" s="114"/>
-      <c r="X35" s="113"/>
-      <c r="Y35" s="114"/>
+      <c r="A35" s="86"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="91"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="93"/>
+      <c r="G35" s="91"/>
+      <c r="H35" s="92"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="96"/>
+      <c r="L35" s="97"/>
+      <c r="M35" s="97"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="97"/>
+      <c r="Q35" s="98"/>
+      <c r="R35" s="86"/>
+      <c r="S35" s="87"/>
+      <c r="T35" s="86"/>
+      <c r="U35" s="100"/>
+      <c r="V35" s="100"/>
+      <c r="W35" s="87"/>
+      <c r="X35" s="86"/>
+      <c r="Y35" s="87"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="s">
@@ -15064,116 +15064,15 @@
     </row>
   </sheetData>
   <mergeCells count="143">
-    <mergeCell ref="X34:Y35"/>
-    <mergeCell ref="A34:B35"/>
-    <mergeCell ref="C34:F35"/>
-    <mergeCell ref="G34:J35"/>
-    <mergeCell ref="K34:Q35"/>
-    <mergeCell ref="R34:S35"/>
-    <mergeCell ref="T34:W35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="K33:Q33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="T33:W33"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="T32:W32"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:W31"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="T30:W30"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:W29"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:W28"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T27:W27"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="X25:Y25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="T23:W23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T22:W22"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="T21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="K18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="T18:W18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="O7:Q8"/>
+    <mergeCell ref="R7:T8"/>
+    <mergeCell ref="U7:W8"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="S10:W10"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="P1:V1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="D2:W2"/>
     <mergeCell ref="D3:W3"/>
@@ -15198,15 +15097,116 @@
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="K14:Q14"/>
     <mergeCell ref="R14:S14"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="O7:Q8"/>
-    <mergeCell ref="R7:T8"/>
-    <mergeCell ref="U7:W8"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="S10:W10"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="K18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T22:W22"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="T21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:W23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="T26:W26"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="T28:W28"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T27:W27"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="T30:W30"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:W29"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="T32:W32"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:W31"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X34:Y35"/>
+    <mergeCell ref="A34:B35"/>
+    <mergeCell ref="C34:F35"/>
+    <mergeCell ref="G34:J35"/>
+    <mergeCell ref="K34:Q35"/>
+    <mergeCell ref="R34:S35"/>
+    <mergeCell ref="T34:W35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="K33:Q33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="T33:W33"/>
+    <mergeCell ref="X33:Y33"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.86614173228346458" right="0.51181102362204722" top="0.59055118110236227" bottom="0.19685039370078741" header="0.59055118110236227" footer="0.19685039370078741"/>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/Pana-CIM管理手順書案_未承認.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nk365-my.sharepoint.com/personal/ss80751_ad_nkc_co_jp/Documents/ドキュメント/Work_Vault/10_業務全般/PanaCIM_LNB/01_成果物/20261015_管理手順書案/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{FC963946-1E0E-4B79-95BF-70F924E5A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0BA3DFE-1660-4BA0-8790-9AEF5E45B834}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{FC963946-1E0E-4B79-95BF-70F924E5A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBA9BC16-D4E6-4214-9AC0-A9C8FBCF82AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="6">月次再起動!$A$1:$AZ$100</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">相関図!$A$1:$AY$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">相関図!$A$1:$AY$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'チェックシート(月次・異常時)'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">バックアップ!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">異常時の対応!$1:$3</definedName>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="393">
   <si>
     <t>手 順 書</t>
   </si>
@@ -1475,10 +1475,16 @@
     <t>確定事項のみ記載。出典：公式資料・操作手順書 0494-912039(06)・会議記録。暫定・未確認の経路は含まない</t>
   </si>
   <si>
-    <t>凡例：【サーバ】=サーバー(VM含む)／【端末(PC)】=作業員が操作するPC／【設備】=製造設備／【表示】=画面・表示装置／【保存領域】=ファイル保存場所。色: 青=サーバ・表示系／黄=PC・操作端末／緑=設備・データ保存</t>
-  </si>
-  <si>
-    <t>配置：A4 縦 1 頁。事象別の図(アンドン・稼働モニタ異常／月次再起動／異常時再起動)は PanaCIM_LNB_確実構成図.drawio に残置。</t>
+    <t>凡例：【サーバ】=サーバー(VM含む)／【端末(PC)】=作業員が操作するPC／【設備】=製造設備／【表示】=画面・表示装置</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　【保存領域】=ファイル保存場所。色: 青=サーバ・表示系／黄=PC・操作端末／緑=設備・データ保存</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>配置：A4縦1頁。事象別の図(アンドン・稼働モニタ異常/月次再起動/異常時再起動)は確実構成図.drawioに残置</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -6555,13 +6561,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>119380</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>104140</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6632,13 +6638,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>119380</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>142240</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6709,13 +6715,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>20320</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>50</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>33020</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6786,13 +6792,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>20320</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>50</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>142240</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6840,10 +6846,10 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="50800" tIns="25400" rIns="76200" bIns="12700" rtlCol="0" anchor="t" anchorCtr="1"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="25400" tIns="25400" rIns="76200" bIns="12700" rtlCol="0" anchor="t" anchorCtr="0"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="l"/>
+          <a:pPr algn="r"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800" b="1">
               <a:solidFill>
@@ -6883,13 +6889,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>20320</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>134620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>50</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6960,13 +6966,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>119380</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>50</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>40640</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7057,13 +7063,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>116840</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>73660</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7164,13 +7170,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>116840</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>5080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7331,13 +7337,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>40640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>10160</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7495,13 +7501,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>111760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>157480</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7649,13 +7655,13 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>17780</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>134620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>49</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>27940</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7776,13 +7782,13 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>17780</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>20320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>49</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7903,13 +7909,13 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>17780</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>119380</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>93980</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8030,13 +8036,13 @@
     <xdr:from>
       <xdr:col>39</xdr:col>
       <xdr:colOff>66040</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>119380</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>49</xdr:col>
       <xdr:colOff>116840</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8137,13 +8143,13 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>17780</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>119380</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>49</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>5080</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -8261,14 +8267,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>17780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>20320</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8284,7 +8290,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="660400" y="7416800"/>
-          <a:ext cx="1397000" cy="482600"/>
+          <a:ext cx="1397000" cy="762000"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -8388,14 +8394,14 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>86360</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>17780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>58420</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>20320</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8411,7 +8417,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2159000" y="7416800"/>
-          <a:ext cx="1397000" cy="482600"/>
+          <a:ext cx="1397000" cy="762000"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -8515,14 +8521,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>119380</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>33020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>50</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>104140</xdr:rowOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>81280</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8538,7 +8544,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="508000" y="8712200"/>
-          <a:ext cx="5969000" cy="711200"/>
+          <a:ext cx="5969000" cy="1168400"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -8872,13 +8878,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>123190</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>73660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>123190</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>40640</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8928,13 +8934,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>48260</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9019,13 +9025,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>81280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>17780</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>66040</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -9075,13 +9081,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>96520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9166,13 +9172,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>17780</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>142240</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -9223,13 +9229,13 @@
       <xdr:col>19</xdr:col>
       <xdr:colOff>78740</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>35560</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9244,8 +9250,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2540000" y="5651500"/>
-          <a:ext cx="863600" cy="139700"/>
+          <a:off x="2540000" y="5562600"/>
+          <a:ext cx="863600" cy="381000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9333,13 +9339,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>17780</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -9389,13 +9395,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>86360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9490,13 +9496,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>17780</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -9546,13 +9552,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>124460</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9637,13 +9643,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>55880</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>119380</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -9693,13 +9699,13 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
       <xdr:colOff>104140</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>5080</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9784,13 +9790,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>119380</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -9840,13 +9846,13 @@
     <xdr:from>
       <xdr:col>40</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>81280</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9931,13 +9937,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>2540</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>74930</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -9987,14 +9993,14 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>73660</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>154940</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>134620</xdr:rowOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>17780</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10009,8 +10015,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4089400" y="3873500"/>
-          <a:ext cx="1168400" cy="139700"/>
+          <a:off x="4089400" y="3810000"/>
+          <a:ext cx="1498600" cy="279400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -20436,7 +20442,7 @@
   <sheetPr>
     <tabColor rgb="FFFFCCFF"/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr defaultColWidth="1.88671875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="50" width="1.88671875" style="1"/>
@@ -20666,6 +20672,11 @@
     <row r="9" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="66" t="s">
         <v>391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C10" s="66" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
